--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_computers_peripherals.xlsx
@@ -1121,43 +1121,43 @@
         <v>4.82456140350877</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>28.3995513385773</v>
       </c>
       <c r="G2">
         <v>1.90909090909091</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.6268181818181821</v>
       </c>
       <c r="I2">
         <v>0.0304568527918782</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>267.4</v>
       </c>
       <c r="L2">
-        <v>277.485239435788</v>
+        <v>274.564867203974</v>
       </c>
       <c r="M2">
         <v>229.3</v>
       </c>
       <c r="N2">
-        <v>230.985239435788</v>
+        <v>230.822867203974</v>
       </c>
       <c r="O2">
         <v>8.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.758</v>
       </c>
       <c r="Q2">
         <v>0.110240627167012</v>
       </c>
       <c r="R2">
-        <v>0.109770476405716</v>
+        <v>0.109815476405716</v>
       </c>
       <c r="S2">
         <v>0.0612366166625341</v>
@@ -1179,13 +1179,13 @@
         <v>0.111780020167152</v>
       </c>
       <c r="X2">
-        <v>0.109770476405716</v>
+        <v>0.110416642834057</v>
       </c>
       <c r="Y2">
         <v>1.28607340160475</v>
       </c>
       <c r="Z2">
-        <v>1.24690365333253</v>
+        <v>1.25949863972983</v>
       </c>
       <c r="AA2">
         <v>8.4</v>
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1097704764057162</v>
+        <v>0.1098154764057162</v>
       </c>
       <c r="C2">
-        <v>277.4852394357878</v>
+        <v>274.5648672039742</v>
       </c>
       <c r="D2">
-        <v>230.9852394357878</v>
+        <v>230.8228672039742</v>
       </c>
       <c r="E2">
-        <v>-8.4</v>
+        <v>-5.642000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.758</v>
       </c>
       <c r="G2">
         <v>46.5</v>
@@ -1439,28 +1439,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1387274</v>
       </c>
       <c r="N2">
-        <v>3.939795918367347</v>
+        <v>3.801068518367347</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>3.939795918367347</v>
+        <v>3.801068518367347</v>
       </c>
       <c r="Q2">
-        <v>4.489795918367347</v>
+        <v>4.351068518367347</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1097704764057162</v>
+        <v>0.1104166428340567</v>
       </c>
       <c r="T2">
-        <v>1.246903653332528</v>
+        <v>1.259498639729826</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>28.3995513385773</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1098154764057162</v>
+        <v>0.1098604764057162</v>
       </c>
       <c r="C3">
-        <v>274.5648672039742</v>
+        <v>271.6447230925506</v>
       </c>
       <c r="D3">
-        <v>230.8228672039742</v>
+        <v>230.6607230925506</v>
       </c>
       <c r="E3">
-        <v>-5.642000000000001</v>
+        <v>-2.884000000000001</v>
       </c>
       <c r="F3">
-        <v>2.758</v>
+        <v>5.515999999999999</v>
       </c>
       <c r="G3">
         <v>46.5</v>
@@ -1521,28 +1521,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M3">
-        <v>0.1387274</v>
+        <v>0.2774547999999999</v>
       </c>
       <c r="N3">
-        <v>3.801068518367347</v>
+        <v>3.662341118367347</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>3.801068518367347</v>
+        <v>3.662341118367347</v>
       </c>
       <c r="Q3">
-        <v>4.351068518367347</v>
+        <v>4.212341118367347</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1104166428340567</v>
+        <v>0.1110759963323635</v>
       </c>
       <c r="T3">
-        <v>1.259498639729826</v>
+        <v>1.272350666665845</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>28.3995513385773</v>
+        <v>14.19977566928865</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1098604764057162</v>
+        <v>0.1100014764057162</v>
       </c>
       <c r="C4">
-        <v>271.6447230925506</v>
+        <v>268.3801434346232</v>
       </c>
       <c r="D4">
-        <v>230.6607230925506</v>
+        <v>230.1541434346231</v>
       </c>
       <c r="E4">
-        <v>-2.884000000000001</v>
+        <v>-0.1260000000000012</v>
       </c>
       <c r="F4">
-        <v>5.515999999999999</v>
+        <v>8.273999999999999</v>
       </c>
       <c r="G4">
         <v>46.5</v>
@@ -1603,45 +1603,45 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M4">
-        <v>0.2774547999999999</v>
+        <v>0.442659</v>
       </c>
       <c r="N4">
-        <v>3.662341118367347</v>
+        <v>3.497136918367347</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>3.662341118367347</v>
+        <v>3.497136918367347</v>
       </c>
       <c r="Q4">
-        <v>4.212341118367347</v>
+        <v>4.047136918367348</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1110759963323635</v>
+        <v>0.111748944748161</v>
       </c>
       <c r="T4">
-        <v>1.272350666665845</v>
+        <v>1.285467683847967</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>14.19977566928865</v>
+        <v>8.900295528538553</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1100014764057162</v>
+        <v>0.1101104764057162</v>
       </c>
       <c r="C5">
-        <v>268.3801434346232</v>
+        <v>265.2320545558514</v>
       </c>
       <c r="D5">
-        <v>230.1541434346231</v>
+        <v>229.7640545558514</v>
       </c>
       <c r="E5">
-        <v>-0.1260000000000012</v>
+        <v>2.631999999999998</v>
       </c>
       <c r="F5">
-        <v>8.273999999999999</v>
+        <v>11.032</v>
       </c>
       <c r="G5">
         <v>46.5</v>
@@ -1685,45 +1685,45 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M5">
-        <v>0.442659</v>
+        <v>0.5990375999999999</v>
       </c>
       <c r="N5">
-        <v>3.497136918367347</v>
+        <v>3.340758318367347</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>3.497136918367347</v>
+        <v>3.340758318367347</v>
       </c>
       <c r="Q5">
-        <v>4.047136918367348</v>
+        <v>3.890758318367348</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.111748944748161</v>
+        <v>0.112435912922621</v>
       </c>
       <c r="T5">
-        <v>1.285467683847967</v>
+        <v>1.298857972221383</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y5">
-        <v>8.900295528538553</v>
+        <v>6.576875839458737</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1101104764057162</v>
+        <v>0.1102454764057162</v>
       </c>
       <c r="C6">
-        <v>265.2320545558514</v>
+        <v>261.9927461833325</v>
       </c>
       <c r="D6">
-        <v>229.7640545558514</v>
+        <v>229.2827461833325</v>
       </c>
       <c r="E6">
-        <v>2.631999999999998</v>
+        <v>5.389999999999999</v>
       </c>
       <c r="F6">
-        <v>11.032</v>
+        <v>13.79</v>
       </c>
       <c r="G6">
         <v>46.5</v>
@@ -1767,45 +1767,45 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M6">
-        <v>0.5990375999999999</v>
+        <v>0.762587</v>
       </c>
       <c r="N6">
-        <v>3.340758318367347</v>
+        <v>3.177208918367347</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>3.340758318367347</v>
+        <v>3.177208918367347</v>
       </c>
       <c r="Q6">
-        <v>3.890758318367348</v>
+        <v>3.727208918367348</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.112435912922621</v>
+        <v>0.1131373435849644</v>
       </c>
       <c r="T6">
-        <v>1.298857972221383</v>
+        <v>1.312530161402661</v>
       </c>
       <c r="U6">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.576875839458737</v>
+        <v>5.1663559939618</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1102454764057162</v>
+        <v>0.1104904764057162</v>
       </c>
       <c r="C7">
-        <v>261.9927461833325</v>
+        <v>258.3663915825314</v>
       </c>
       <c r="D7">
-        <v>229.2827461833325</v>
+        <v>228.4143915825314</v>
       </c>
       <c r="E7">
-        <v>5.389999999999999</v>
+        <v>8.147999999999998</v>
       </c>
       <c r="F7">
-        <v>13.79</v>
+        <v>16.548</v>
       </c>
       <c r="G7">
         <v>46.5</v>
@@ -1849,45 +1849,45 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M7">
-        <v>0.762587</v>
+        <v>0.9564743999999999</v>
       </c>
       <c r="N7">
-        <v>3.177208918367347</v>
+        <v>2.983321518367347</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>3.177208918367347</v>
+        <v>2.983321518367347</v>
       </c>
       <c r="Q7">
-        <v>3.727208918367348</v>
+        <v>3.533321518367348</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1131373435849644</v>
+        <v>0.1138536983039534</v>
       </c>
       <c r="T7">
-        <v>1.312530161402661</v>
+        <v>1.326493248226093</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y7">
-        <v>5.1663559939618</v>
+        <v>4.119081408103916</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1104904764057162</v>
+        <v>0.1110514764057162</v>
       </c>
       <c r="C8">
-        <v>258.3663915825314</v>
+        <v>253.6445973400677</v>
       </c>
       <c r="D8">
-        <v>228.4143915825314</v>
+        <v>226.4505973400677</v>
       </c>
       <c r="E8">
-        <v>8.147999999999998</v>
+        <v>10.90599999999999</v>
       </c>
       <c r="F8">
-        <v>16.548</v>
+        <v>19.30599999999999</v>
       </c>
       <c r="G8">
         <v>46.5</v>
@@ -1931,45 +1931,45 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M8">
-        <v>0.9564743999999999</v>
+        <v>1.2375146</v>
       </c>
       <c r="N8">
-        <v>2.983321518367347</v>
+        <v>2.702281318367348</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.983321518367347</v>
+        <v>2.702281318367348</v>
       </c>
       <c r="Q8">
-        <v>3.533321518367348</v>
+        <v>3.252281318367348</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1138536983039534</v>
+        <v>0.1145854585007701</v>
       </c>
       <c r="T8">
-        <v>1.326493248226093</v>
+        <v>1.340756616486589</v>
       </c>
       <c r="U8">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.119081408103916</v>
+        <v>3.183635908915619</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1110514764057162</v>
+        <v>0.1121704764057162</v>
       </c>
       <c r="C9">
-        <v>253.6445973400678</v>
+        <v>247.0686615326684</v>
       </c>
       <c r="D9">
-        <v>226.4505973400678</v>
+        <v>222.6326615326684</v>
       </c>
       <c r="E9">
-        <v>10.906</v>
+        <v>13.664</v>
       </c>
       <c r="F9">
-        <v>19.306</v>
+        <v>22.064</v>
       </c>
       <c r="G9">
         <v>46.5</v>
@@ -2013,45 +2013,45 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M9">
-        <v>1.2375146</v>
+        <v>1.6724512</v>
       </c>
       <c r="N9">
-        <v>2.702281318367347</v>
+        <v>2.267344718367347</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.702281318367347</v>
+        <v>2.267344718367347</v>
       </c>
       <c r="Q9">
-        <v>3.252281318367348</v>
+        <v>2.817344718367348</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1145854585007701</v>
+        <v>0.1153331265279524</v>
       </c>
       <c r="T9">
-        <v>1.340756616486589</v>
+        <v>1.355330057970139</v>
       </c>
       <c r="U9">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y9">
-        <v>3.183635908915618</v>
+        <v>2.355701570465762</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1121704764057162</v>
+        <v>0.1124704764057162</v>
       </c>
       <c r="C10">
-        <v>247.0686615326684</v>
+        <v>243.3088718041332</v>
       </c>
       <c r="D10">
-        <v>222.6326615326684</v>
+        <v>221.6308718041332</v>
       </c>
       <c r="E10">
-        <v>13.664</v>
+        <v>16.422</v>
       </c>
       <c r="F10">
-        <v>22.064</v>
+        <v>24.822</v>
       </c>
       <c r="G10">
         <v>46.5</v>
@@ -2095,28 +2095,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M10">
-        <v>1.6724512</v>
+        <v>1.8815076</v>
       </c>
       <c r="N10">
-        <v>2.267344718367347</v>
+        <v>2.058288318367348</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.267344718367347</v>
+        <v>2.058288318367348</v>
       </c>
       <c r="Q10">
-        <v>2.817344718367348</v>
+        <v>2.608288318367348</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1153331265279524</v>
+        <v>0.1160972268194683</v>
       </c>
       <c r="T10">
-        <v>1.355330057970139</v>
+        <v>1.37022379487091</v>
       </c>
       <c r="U10">
         <v>0.07580000000000001</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>2.355701570465762</v>
+        <v>2.093956951525122</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,81 +2141,81 @@
     </row>
     <row r="11">
       <c r="A11">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="B11">
+        <v>0.1141904764057162</v>
+      </c>
+      <c r="C11">
+        <v>234.9769217523502</v>
+      </c>
+      <c r="D11">
+        <v>216.0569217523502</v>
+      </c>
+      <c r="E11">
+        <v>19.17999999999999</v>
+      </c>
+      <c r="F11">
+        <v>27.57999999999999</v>
+      </c>
+      <c r="G11">
+        <v>46.5</v>
+      </c>
+      <c r="H11">
+        <v>267.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>4.489795918367347</v>
+      </c>
+      <c r="K11">
+        <v>0.5500000000000003</v>
+      </c>
+      <c r="L11">
+        <v>3.939795918367347</v>
+      </c>
+      <c r="M11">
+        <v>2.482199999999999</v>
+      </c>
+      <c r="N11">
+        <v>1.457595918367348</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.457595918367348</v>
+      </c>
+      <c r="Q11">
+        <v>2.007595918367348</v>
+      </c>
+      <c r="R11">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S11">
+        <v>0.1168783071174624</v>
+      </c>
+      <c r="T11">
+        <v>1.385448503702809</v>
+      </c>
+      <c r="U11">
         <v>0.09</v>
       </c>
-      <c r="B11">
-        <v>0.1124704764057162</v>
-      </c>
-      <c r="C11">
-        <v>243.3088718041332</v>
-      </c>
-      <c r="D11">
-        <v>221.6308718041332</v>
-      </c>
-      <c r="E11">
-        <v>16.422</v>
-      </c>
-      <c r="F11">
-        <v>24.822</v>
-      </c>
-      <c r="G11">
-        <v>46.5</v>
-      </c>
-      <c r="H11">
-        <v>267.4</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>4.489795918367347</v>
-      </c>
-      <c r="K11">
-        <v>0.5500000000000003</v>
-      </c>
-      <c r="L11">
-        <v>3.939795918367347</v>
-      </c>
-      <c r="M11">
-        <v>1.8815076</v>
-      </c>
-      <c r="N11">
-        <v>2.058288318367348</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>2.058288318367348</v>
-      </c>
-      <c r="Q11">
-        <v>2.608288318367348</v>
-      </c>
-      <c r="R11">
-        <v>0.0989010989010989</v>
-      </c>
-      <c r="S11">
-        <v>0.1160972268194683</v>
-      </c>
-      <c r="T11">
-        <v>1.37022379487091</v>
-      </c>
-      <c r="U11">
-        <v>0.07580000000000001</v>
-      </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.093956951525122</v>
+        <v>1.587219369256042</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1141904764057162</v>
+        <v>0.1208804764057162</v>
       </c>
       <c r="C12">
-        <v>234.9769217523502</v>
+        <v>212.9673016812077</v>
       </c>
       <c r="D12">
-        <v>216.0569217523502</v>
+        <v>196.8053016812077</v>
       </c>
       <c r="E12">
-        <v>19.18</v>
+        <v>21.938</v>
       </c>
       <c r="F12">
-        <v>27.58</v>
+        <v>30.33799999999999</v>
       </c>
       <c r="G12">
         <v>46.5</v>
@@ -2259,45 +2259,45 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M12">
-        <v>2.4822</v>
+        <v>4.4536184</v>
       </c>
       <c r="N12">
-        <v>1.457595918367347</v>
+        <v>-0.5138224816326527</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>1.457595918367347</v>
+        <v>-0.5138224816326527</v>
       </c>
       <c r="Q12">
-        <v>2.007595918367348</v>
+        <v>0.03617751836734762</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1168783071174624</v>
+        <v>0.1176769397817036</v>
       </c>
       <c r="T12">
-        <v>1.385448503702809</v>
+        <v>1.401015340823065</v>
       </c>
       <c r="U12">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y12">
-        <v>1.587219369256042</v>
+        <v>0.8846280854164217</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1208804764057162</v>
+        <v>0.1218904764057162</v>
       </c>
       <c r="C13">
-        <v>212.9673016812077</v>
+        <v>207.5969727264229</v>
       </c>
       <c r="D13">
-        <v>196.8053016812077</v>
+        <v>194.1929727264229</v>
       </c>
       <c r="E13">
-        <v>21.938</v>
+        <v>24.696</v>
       </c>
       <c r="F13">
-        <v>30.33799999999999</v>
+        <v>33.096</v>
       </c>
       <c r="G13">
         <v>46.5</v>
@@ -2341,28 +2341,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M13">
-        <v>4.4536184</v>
+        <v>4.8584928</v>
       </c>
       <c r="N13">
-        <v>-0.5138224816326527</v>
+        <v>-0.9186968816326524</v>
       </c>
       <c r="O13">
         <v>-0</v>
       </c>
       <c r="P13">
-        <v>-0.5138224816326527</v>
+        <v>-0.9186968816326524</v>
       </c>
       <c r="Q13">
-        <v>0.03617751836734762</v>
+        <v>-0.3686968816326521</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1176769397817036</v>
+        <v>0.1184937231883138</v>
       </c>
       <c r="T13">
-        <v>1.401015340823065</v>
+        <v>1.416935969696054</v>
       </c>
       <c r="U13">
         <v>0.1468</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.8846280854164217</v>
+        <v>0.8109090782983865</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1218904764057162</v>
+        <v>0.1299204764057162</v>
       </c>
       <c r="C14">
-        <v>207.5969727264229</v>
+        <v>186.3016363058316</v>
       </c>
       <c r="D14">
-        <v>194.1929727264229</v>
+        <v>175.6556363058315</v>
       </c>
       <c r="E14">
-        <v>24.696</v>
+        <v>27.45399999999999</v>
       </c>
       <c r="F14">
-        <v>33.096</v>
+        <v>35.85399999999999</v>
       </c>
       <c r="G14">
         <v>46.5</v>
@@ -2423,45 +2423,45 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M14">
-        <v>4.8584928</v>
+        <v>7.199483199999999</v>
       </c>
       <c r="N14">
-        <v>-0.9186968816326524</v>
+        <v>-3.259687281632651</v>
       </c>
       <c r="O14">
         <v>-0</v>
       </c>
       <c r="P14">
-        <v>-0.9186968816326524</v>
+        <v>-3.259687281632651</v>
       </c>
       <c r="Q14">
-        <v>-0.3686968816326521</v>
+        <v>-2.709687281632651</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1184937231883138</v>
+        <v>0.1193292832249611</v>
       </c>
       <c r="T14">
-        <v>1.416935969696054</v>
+        <v>1.433222590037388</v>
       </c>
       <c r="U14">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y14">
-        <v>0.8109090782983865</v>
+        <v>0.547233156730937</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1299204764057162</v>
+        <v>0.1314704764057162</v>
       </c>
       <c r="C15">
-        <v>186.3016363058316</v>
+        <v>180.365572546916</v>
       </c>
       <c r="D15">
-        <v>175.6556363058315</v>
+        <v>172.477572546916</v>
       </c>
       <c r="E15">
-        <v>27.45399999999999</v>
+        <v>30.212</v>
       </c>
       <c r="F15">
-        <v>35.85399999999999</v>
+        <v>38.61199999999999</v>
       </c>
       <c r="G15">
         <v>46.5</v>
@@ -2505,28 +2505,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M15">
-        <v>7.199483199999999</v>
+        <v>7.7532896</v>
       </c>
       <c r="N15">
-        <v>-3.259687281632651</v>
+        <v>-3.813493681632652</v>
       </c>
       <c r="O15">
         <v>-0</v>
       </c>
       <c r="P15">
-        <v>-3.259687281632651</v>
+        <v>-3.813493681632652</v>
       </c>
       <c r="Q15">
-        <v>-2.709687281632651</v>
+        <v>-3.263493681632652</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1193292832249611</v>
+        <v>0.1201842748903676</v>
       </c>
       <c r="T15">
-        <v>1.433222590037388</v>
+        <v>1.449887968991311</v>
       </c>
       <c r="U15">
         <v>0.2008</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.547233156730937</v>
+        <v>0.5081450741072986</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1314704764057162</v>
+        <v>0.1382704764057162</v>
       </c>
       <c r="C16">
-        <v>180.365572546916</v>
+        <v>164.9240919495723</v>
       </c>
       <c r="D16">
-        <v>172.477572546916</v>
+        <v>159.7940919495723</v>
       </c>
       <c r="E16">
-        <v>30.212</v>
+        <v>32.97</v>
       </c>
       <c r="F16">
-        <v>38.61199999999999</v>
+        <v>41.37</v>
       </c>
       <c r="G16">
         <v>46.5</v>
@@ -2587,45 +2587,45 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M16">
-        <v>7.7532896</v>
+        <v>9.755046</v>
       </c>
       <c r="N16">
-        <v>-3.813493681632652</v>
+        <v>-5.815250081632653</v>
       </c>
       <c r="O16">
         <v>-0</v>
       </c>
       <c r="P16">
-        <v>-3.813493681632652</v>
+        <v>-5.815250081632653</v>
       </c>
       <c r="Q16">
-        <v>-3.263493681632652</v>
+        <v>-5.265250081632653</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1201842748903676</v>
+        <v>0.1210593840067249</v>
       </c>
       <c r="T16">
-        <v>1.449887968991311</v>
+        <v>1.466945474508856</v>
       </c>
       <c r="U16">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.5081450741072986</v>
+        <v>0.4038726130422498</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1382704764057162</v>
+        <v>0.1401704764057162</v>
       </c>
       <c r="C17">
-        <v>164.9240919495724</v>
+        <v>158.9488911229185</v>
       </c>
       <c r="D17">
-        <v>159.7940919495723</v>
+        <v>156.5768911229185</v>
       </c>
       <c r="E17">
-        <v>32.96999999999999</v>
+        <v>35.72799999999999</v>
       </c>
       <c r="F17">
-        <v>41.36999999999999</v>
+        <v>44.12799999999999</v>
       </c>
       <c r="G17">
         <v>46.5</v>
@@ -2669,28 +2669,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M17">
-        <v>9.755045999999998</v>
+        <v>10.4053824</v>
       </c>
       <c r="N17">
-        <v>-5.815250081632652</v>
+        <v>-6.465586481632652</v>
       </c>
       <c r="O17">
         <v>-0</v>
       </c>
       <c r="P17">
-        <v>-5.815250081632652</v>
+        <v>-6.465586481632652</v>
       </c>
       <c r="Q17">
-        <v>-5.265250081632651</v>
+        <v>-5.915586481632651</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1210593840067249</v>
+        <v>0.121955329054424</v>
       </c>
       <c r="T17">
-        <v>1.466945474508856</v>
+        <v>1.484409111110152</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.4038726130422499</v>
+        <v>0.3786305747271093</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1401704764057162</v>
+        <v>0.1420704764057162</v>
       </c>
       <c r="C18">
-        <v>158.9488911229185</v>
+        <v>153.1006800401375</v>
       </c>
       <c r="D18">
-        <v>156.5768911229185</v>
+        <v>153.4866800401375</v>
       </c>
       <c r="E18">
-        <v>35.72799999999999</v>
+        <v>38.486</v>
       </c>
       <c r="F18">
-        <v>44.12799999999999</v>
+        <v>46.886</v>
       </c>
       <c r="G18">
         <v>46.5</v>
@@ -2751,28 +2751,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M18">
-        <v>10.4053824</v>
+        <v>11.0557188</v>
       </c>
       <c r="N18">
-        <v>-6.465586481632652</v>
+        <v>-7.115922881632653</v>
       </c>
       <c r="O18">
         <v>-0</v>
       </c>
       <c r="P18">
-        <v>-6.465586481632652</v>
+        <v>-7.115922881632653</v>
       </c>
       <c r="Q18">
-        <v>-5.915586481632651</v>
+        <v>-6.565922881632652</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.121955329054424</v>
+        <v>0.1228728631394171</v>
       </c>
       <c r="T18">
-        <v>1.484409111110152</v>
+        <v>1.502293558231961</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.3786305747271093</v>
+        <v>0.3563581879784558</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1420704764057162</v>
+        <v>0.1439704764057162</v>
       </c>
       <c r="C19">
-        <v>153.1006800401375</v>
+        <v>147.3720853893481</v>
       </c>
       <c r="D19">
-        <v>153.4866800401375</v>
+        <v>150.5160853893481</v>
       </c>
       <c r="E19">
-        <v>38.486</v>
+        <v>41.244</v>
       </c>
       <c r="F19">
-        <v>46.886</v>
+        <v>49.644</v>
       </c>
       <c r="G19">
         <v>46.5</v>
@@ -2833,28 +2833,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M19">
-        <v>11.0557188</v>
+        <v>11.7060552</v>
       </c>
       <c r="N19">
-        <v>-7.115922881632653</v>
+        <v>-7.766259281632653</v>
       </c>
       <c r="O19">
         <v>-0</v>
       </c>
       <c r="P19">
-        <v>-7.115922881632653</v>
+        <v>-7.766259281632653</v>
       </c>
       <c r="Q19">
-        <v>-6.565922881632652</v>
+        <v>-7.216259281632652</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1228728631394171</v>
+        <v>0.1238127761045319</v>
       </c>
       <c r="T19">
-        <v>1.502293558231961</v>
+        <v>1.520614211381131</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3563581879784558</v>
+        <v>0.3365605108685416</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1439704764057162</v>
+        <v>0.1458704764057162</v>
       </c>
       <c r="C20">
-        <v>147.3720853893482</v>
+        <v>141.7562938357204</v>
       </c>
       <c r="D20">
-        <v>150.5160853893481</v>
+        <v>147.6582938357204</v>
       </c>
       <c r="E20">
-        <v>41.24399999999999</v>
+        <v>44.002</v>
       </c>
       <c r="F20">
-        <v>49.64399999999999</v>
+        <v>52.40199999999999</v>
       </c>
       <c r="G20">
         <v>46.5</v>
@@ -2915,28 +2915,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M20">
-        <v>11.7060552</v>
+        <v>12.3563916</v>
       </c>
       <c r="N20">
-        <v>-7.766259281632651</v>
+        <v>-8.416595681632652</v>
       </c>
       <c r="O20">
         <v>-0</v>
       </c>
       <c r="P20">
-        <v>-7.766259281632651</v>
+        <v>-8.416595681632652</v>
       </c>
       <c r="Q20">
-        <v>-7.216259281632651</v>
+        <v>-7.866595681632651</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1238127761045319</v>
+        <v>0.1247758967971805</v>
       </c>
       <c r="T20">
-        <v>1.520614211381131</v>
+        <v>1.539387226336454</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3365605108685416</v>
+        <v>0.3188467997701973</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1458704764057162</v>
+        <v>0.1477704764057162</v>
       </c>
       <c r="C21">
-        <v>141.7562938357204</v>
+        <v>136.2469998516497</v>
       </c>
       <c r="D21">
-        <v>147.6582938357204</v>
+        <v>144.9069998516497</v>
       </c>
       <c r="E21">
-        <v>44.002</v>
+        <v>46.76</v>
       </c>
       <c r="F21">
-        <v>52.40199999999999</v>
+        <v>55.16</v>
       </c>
       <c r="G21">
         <v>46.5</v>
@@ -2997,28 +2997,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M21">
-        <v>12.3563916</v>
+        <v>13.006728</v>
       </c>
       <c r="N21">
-        <v>-8.416595681632652</v>
+        <v>-9.066932081632652</v>
       </c>
       <c r="O21">
         <v>-0</v>
       </c>
       <c r="P21">
-        <v>-8.416595681632652</v>
+        <v>-9.066932081632652</v>
       </c>
       <c r="Q21">
-        <v>-7.866595681632651</v>
+        <v>-8.516932081632651</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1247758967971805</v>
+        <v>0.1257630955071452</v>
       </c>
       <c r="T21">
-        <v>1.539387226336454</v>
+        <v>1.55862956666566</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3188467997701973</v>
+        <v>0.3029044597816873</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1477704764057162</v>
+        <v>0.1496704764057162</v>
       </c>
       <c r="C22">
-        <v>136.2469998516497</v>
+        <v>130.8383592726778</v>
       </c>
       <c r="D22">
-        <v>144.9069998516497</v>
+        <v>142.2563592726778</v>
       </c>
       <c r="E22">
-        <v>46.76</v>
+        <v>49.518</v>
       </c>
       <c r="F22">
-        <v>55.16</v>
+        <v>57.918</v>
       </c>
       <c r="G22">
         <v>46.5</v>
@@ -3079,28 +3079,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M22">
-        <v>13.006728</v>
+        <v>13.6570644</v>
       </c>
       <c r="N22">
-        <v>-9.066932081632652</v>
+        <v>-9.717268481632654</v>
       </c>
       <c r="O22">
         <v>-0</v>
       </c>
       <c r="P22">
-        <v>-9.066932081632652</v>
+        <v>-9.717268481632654</v>
       </c>
       <c r="Q22">
-        <v>-8.516932081632651</v>
+        <v>-9.167268481632654</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1257630955071452</v>
+        <v>0.1267752865895142</v>
       </c>
       <c r="T22">
-        <v>1.55862956666566</v>
+        <v>1.578359054851301</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3029044597816873</v>
+        <v>0.2884804378873213</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1496704764057162</v>
+        <v>0.1515704764057162</v>
       </c>
       <c r="C23">
-        <v>130.8383592726778</v>
+        <v>125.5249478591817</v>
       </c>
       <c r="D23">
-        <v>142.2563592726778</v>
+        <v>139.7009478591817</v>
       </c>
       <c r="E23">
-        <v>49.51799999999999</v>
+        <v>52.27599999999999</v>
       </c>
       <c r="F23">
-        <v>57.91799999999999</v>
+        <v>60.67599999999999</v>
       </c>
       <c r="G23">
         <v>46.5</v>
@@ -3161,28 +3161,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M23">
-        <v>13.6570644</v>
+        <v>14.3074008</v>
       </c>
       <c r="N23">
-        <v>-9.717268481632651</v>
+        <v>-10.36760488163265</v>
       </c>
       <c r="O23">
         <v>-0</v>
       </c>
       <c r="P23">
-        <v>-9.717268481632651</v>
+        <v>-10.36760488163265</v>
       </c>
       <c r="Q23">
-        <v>-9.16726848163265</v>
+        <v>-9.817604881632651</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1267752865895142</v>
+        <v>0.1278134312893797</v>
       </c>
       <c r="T23">
-        <v>1.578359054851301</v>
+        <v>1.598594427349394</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2884804378873214</v>
+        <v>0.2753676907106249</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1515704764057162</v>
+        <v>0.1534704764057162</v>
       </c>
       <c r="C24">
-        <v>125.5249478591817</v>
+        <v>120.3017242454934</v>
       </c>
       <c r="D24">
-        <v>139.7009478591817</v>
+        <v>137.2357242454934</v>
       </c>
       <c r="E24">
-        <v>52.27599999999999</v>
+        <v>55.03399999999999</v>
       </c>
       <c r="F24">
-        <v>60.67599999999999</v>
+        <v>63.43399999999999</v>
       </c>
       <c r="G24">
         <v>46.5</v>
@@ -3243,28 +3243,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M24">
-        <v>14.3074008</v>
+        <v>14.9577372</v>
       </c>
       <c r="N24">
-        <v>-10.36760488163265</v>
+        <v>-11.01794128163265</v>
       </c>
       <c r="O24">
         <v>-0</v>
       </c>
       <c r="P24">
-        <v>-10.36760488163265</v>
+        <v>-11.01794128163265</v>
       </c>
       <c r="Q24">
-        <v>-9.817604881632651</v>
+        <v>-10.46794128163265</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1278134312893797</v>
+        <v>0.1288785407866444</v>
       </c>
       <c r="T24">
-        <v>1.598594427349394</v>
+        <v>1.619355393938348</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2753676907106249</v>
+        <v>0.2633951824188586</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1534704764057162</v>
+        <v>0.1553704764057162</v>
       </c>
       <c r="C25">
-        <v>120.3017242454934</v>
+        <v>115.1639967438903</v>
       </c>
       <c r="D25">
-        <v>137.2357242454934</v>
+        <v>134.8559967438903</v>
       </c>
       <c r="E25">
-        <v>55.03399999999999</v>
+        <v>57.79199999999999</v>
       </c>
       <c r="F25">
-        <v>63.43399999999999</v>
+        <v>66.19199999999999</v>
       </c>
       <c r="G25">
         <v>46.5</v>
@@ -3325,28 +3325,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M25">
-        <v>14.9577372</v>
+        <v>15.6080736</v>
       </c>
       <c r="N25">
-        <v>-11.01794128163265</v>
+        <v>-11.66827768163265</v>
       </c>
       <c r="O25">
         <v>-0</v>
       </c>
       <c r="P25">
-        <v>-11.01794128163265</v>
+        <v>-11.66827768163265</v>
       </c>
       <c r="Q25">
-        <v>-10.46794128163265</v>
+        <v>-11.11827768163265</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1288785407866444</v>
+        <v>0.1299716794812055</v>
       </c>
       <c r="T25">
-        <v>1.619355393938348</v>
+        <v>1.640662701753326</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2633951824188586</v>
+        <v>0.2524203831514061</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1553704764057162</v>
+        <v>0.1572704764057162</v>
       </c>
       <c r="C26">
-        <v>115.1639967438903</v>
+        <v>110.1073935435163</v>
       </c>
       <c r="D26">
-        <v>134.8559967438903</v>
+        <v>132.5573935435163</v>
       </c>
       <c r="E26">
-        <v>57.79199999999999</v>
+        <v>60.54999999999999</v>
       </c>
       <c r="F26">
-        <v>66.19199999999999</v>
+        <v>68.94999999999999</v>
       </c>
       <c r="G26">
         <v>46.5</v>
@@ -3407,28 +3407,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M26">
-        <v>15.6080736</v>
+        <v>16.25841</v>
       </c>
       <c r="N26">
-        <v>-11.66827768163265</v>
+        <v>-12.31861408163265</v>
       </c>
       <c r="O26">
         <v>-0</v>
       </c>
       <c r="P26">
-        <v>-11.66827768163265</v>
+        <v>-12.31861408163265</v>
       </c>
       <c r="Q26">
-        <v>-11.11827768163265</v>
+        <v>-11.76861408163265</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1299716794812055</v>
+        <v>0.1310939685409549</v>
       </c>
       <c r="T26">
-        <v>1.640662701753326</v>
+        <v>1.66253820444337</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2524203831514061</v>
+        <v>0.2423235678253499</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1572704764057162</v>
+        <v>0.1591704764057162</v>
       </c>
       <c r="C27">
-        <v>110.1073935435163</v>
+        <v>105.1278359059585</v>
       </c>
       <c r="D27">
-        <v>132.5573935435163</v>
+        <v>130.3358359059585</v>
       </c>
       <c r="E27">
-        <v>60.54999999999999</v>
+        <v>63.30799999999999</v>
       </c>
       <c r="F27">
-        <v>68.94999999999999</v>
+        <v>71.70799999999998</v>
       </c>
       <c r="G27">
         <v>46.5</v>
@@ -3489,28 +3489,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M27">
-        <v>16.25841</v>
+        <v>16.9087464</v>
       </c>
       <c r="N27">
-        <v>-12.31861408163265</v>
+        <v>-12.96895048163265</v>
       </c>
       <c r="O27">
         <v>-0</v>
       </c>
       <c r="P27">
-        <v>-12.31861408163265</v>
+        <v>-12.96895048163265</v>
       </c>
       <c r="Q27">
-        <v>-11.76861408163265</v>
+        <v>-12.41895048163265</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1310939685409549</v>
+        <v>0.1322465897374543</v>
       </c>
       <c r="T27">
-        <v>1.66253820444337</v>
+        <v>1.685004936935848</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2423235678253499</v>
+        <v>0.233003430601298</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1591704764057162</v>
+        <v>0.1610704764057162</v>
       </c>
       <c r="C28">
-        <v>105.1278359059585</v>
+        <v>100.2215140117233</v>
       </c>
       <c r="D28">
-        <v>130.3358359059585</v>
+        <v>128.1875140117233</v>
       </c>
       <c r="E28">
-        <v>63.30799999999999</v>
+        <v>66.06599999999999</v>
       </c>
       <c r="F28">
-        <v>71.70799999999998</v>
+        <v>74.46599999999999</v>
       </c>
       <c r="G28">
         <v>46.5</v>
@@ -3571,28 +3571,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M28">
-        <v>16.9087464</v>
+        <v>17.5590828</v>
       </c>
       <c r="N28">
-        <v>-12.96895048163265</v>
+        <v>-13.61928688163265</v>
       </c>
       <c r="O28">
         <v>-0</v>
       </c>
       <c r="P28">
-        <v>-12.96895048163265</v>
+        <v>-13.61928688163265</v>
       </c>
       <c r="Q28">
-        <v>-12.41895048163265</v>
+        <v>-13.06928688163265</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1322465897374543</v>
+        <v>0.1334307895968715</v>
       </c>
       <c r="T28">
-        <v>1.685004936935848</v>
+        <v>1.708087196345929</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.233003430601298</v>
+        <v>0.2243736739123611</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1610704764057162</v>
+        <v>0.1629704764057162</v>
       </c>
       <c r="C29">
-        <v>100.2215140117233</v>
+        <v>95.3848651567086</v>
       </c>
       <c r="D29">
-        <v>128.1875140117233</v>
+        <v>126.1088651567086</v>
       </c>
       <c r="E29">
-        <v>66.06599999999999</v>
+        <v>68.82399999999998</v>
       </c>
       <c r="F29">
-        <v>74.46599999999999</v>
+        <v>77.22399999999999</v>
       </c>
       <c r="G29">
         <v>46.5</v>
@@ -3653,28 +3653,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M29">
-        <v>17.5590828</v>
+        <v>18.2094192</v>
       </c>
       <c r="N29">
-        <v>-13.61928688163265</v>
+        <v>-14.26962328163265</v>
       </c>
       <c r="O29">
         <v>-0</v>
       </c>
       <c r="P29">
-        <v>-13.61928688163265</v>
+        <v>-14.26962328163265</v>
       </c>
       <c r="Q29">
-        <v>-13.06928688163265</v>
+        <v>-13.71962328163265</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1334307895968715</v>
+        <v>0.134647883896828</v>
       </c>
       <c r="T29">
-        <v>1.708087196345929</v>
+        <v>1.731810629628511</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2243736739123611</v>
+        <v>0.216360328415491</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1629704764057162</v>
+        <v>0.1648704764057162</v>
       </c>
       <c r="C30">
-        <v>95.3848651567086</v>
+        <v>90.61455403618092</v>
       </c>
       <c r="D30">
-        <v>126.1088651567086</v>
+        <v>124.0965540361809</v>
       </c>
       <c r="E30">
-        <v>68.82399999999998</v>
+        <v>71.58199999999999</v>
       </c>
       <c r="F30">
-        <v>77.22399999999999</v>
+        <v>79.982</v>
       </c>
       <c r="G30">
         <v>46.5</v>
@@ -3735,28 +3735,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M30">
-        <v>18.2094192</v>
+        <v>18.8597556</v>
       </c>
       <c r="N30">
-        <v>-14.26962328163265</v>
+        <v>-14.91995968163265</v>
       </c>
       <c r="O30">
         <v>-0</v>
       </c>
       <c r="P30">
-        <v>-14.26962328163265</v>
+        <v>-14.91995968163265</v>
       </c>
       <c r="Q30">
-        <v>-13.71962328163265</v>
+        <v>-14.36995968163265</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.134647883896828</v>
+        <v>0.1358992625432622</v>
       </c>
       <c r="T30">
-        <v>1.731810629628511</v>
+        <v>1.756202328637363</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.216360328415491</v>
+        <v>0.2088996274356465</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1648704764057162</v>
+        <v>0.1667704764057162</v>
       </c>
       <c r="C31">
-        <v>90.61455403618099</v>
+        <v>85.90745488674915</v>
       </c>
       <c r="D31">
-        <v>124.096554036181</v>
+        <v>122.1474548867491</v>
       </c>
       <c r="E31">
-        <v>71.58199999999998</v>
+        <v>74.33999999999997</v>
       </c>
       <c r="F31">
-        <v>79.98199999999999</v>
+        <v>82.73999999999998</v>
       </c>
       <c r="G31">
         <v>46.5</v>
@@ -3817,28 +3817,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M31">
-        <v>18.8597556</v>
+        <v>19.510092</v>
       </c>
       <c r="N31">
-        <v>-14.91995968163265</v>
+        <v>-15.57029608163265</v>
       </c>
       <c r="O31">
         <v>-0</v>
       </c>
       <c r="P31">
-        <v>-14.91995968163265</v>
+        <v>-15.57029608163265</v>
       </c>
       <c r="Q31">
-        <v>-14.36995968163265</v>
+        <v>-15.02029608163265</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1358992625432622</v>
+        <v>0.1371863948653088</v>
       </c>
       <c r="T31">
-        <v>1.756202328637363</v>
+        <v>1.781290933332182</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2088996274356465</v>
+        <v>0.2019363065211249</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1667704764057162</v>
+        <v>0.1686704764057162</v>
       </c>
       <c r="C32">
-        <v>85.90745488674915</v>
+        <v>81.2606352852161</v>
       </c>
       <c r="D32">
-        <v>122.1474548867491</v>
+        <v>120.2586352852161</v>
       </c>
       <c r="E32">
-        <v>74.33999999999997</v>
+        <v>77.09799999999998</v>
       </c>
       <c r="F32">
-        <v>82.73999999999998</v>
+        <v>85.49799999999999</v>
       </c>
       <c r="G32">
         <v>46.5</v>
@@ -3899,28 +3899,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M32">
-        <v>19.510092</v>
+        <v>20.1604284</v>
       </c>
       <c r="N32">
-        <v>-15.57029608163265</v>
+        <v>-16.22063248163265</v>
       </c>
       <c r="O32">
         <v>-0</v>
       </c>
       <c r="P32">
-        <v>-15.57029608163265</v>
+        <v>-16.22063248163265</v>
       </c>
       <c r="Q32">
-        <v>-15.02029608163265</v>
+        <v>-15.67063248163265</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1371863948653088</v>
+        <v>0.1385108353706032</v>
       </c>
       <c r="T32">
-        <v>1.781290933332182</v>
+        <v>1.807106743960185</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2019363065211249</v>
+        <v>0.1954222321172178</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1686704764057162</v>
+        <v>0.1705704764057162</v>
       </c>
       <c r="C33">
-        <v>81.2606352852161</v>
+        <v>76.67134142769383</v>
       </c>
       <c r="D33">
-        <v>120.2586352852161</v>
+        <v>118.4273414276938</v>
       </c>
       <c r="E33">
-        <v>77.09799999999998</v>
+        <v>79.85599999999998</v>
       </c>
       <c r="F33">
-        <v>85.49799999999999</v>
+        <v>88.25599999999999</v>
       </c>
       <c r="G33">
         <v>46.5</v>
@@ -3981,28 +3981,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M33">
-        <v>20.1604284</v>
+        <v>20.8107648</v>
       </c>
       <c r="N33">
-        <v>-16.22063248163265</v>
+        <v>-16.87096888163265</v>
       </c>
       <c r="O33">
         <v>-0</v>
       </c>
       <c r="P33">
-        <v>-16.22063248163265</v>
+        <v>-16.87096888163265</v>
       </c>
       <c r="Q33">
-        <v>-15.67063248163265</v>
+        <v>-16.32096888163265</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1385108353706032</v>
+        <v>0.1398742300084062</v>
       </c>
       <c r="T33">
-        <v>1.807106743960185</v>
+        <v>1.83368184313607</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1954222321172178</v>
+        <v>0.1893152873635547</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1705704764057162</v>
+        <v>0.1724704764057162</v>
       </c>
       <c r="C34">
-        <v>76.67134142769383</v>
+        <v>72.13698473355841</v>
       </c>
       <c r="D34">
-        <v>118.4273414276938</v>
+        <v>116.6509847335584</v>
       </c>
       <c r="E34">
-        <v>79.85599999999998</v>
+        <v>82.61399999999999</v>
       </c>
       <c r="F34">
-        <v>88.25599999999999</v>
+        <v>91.014</v>
       </c>
       <c r="G34">
         <v>46.5</v>
@@ -4063,28 +4063,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M34">
-        <v>20.8107648</v>
+        <v>21.4611012</v>
       </c>
       <c r="N34">
-        <v>-16.87096888163265</v>
+        <v>-17.52130528163265</v>
       </c>
       <c r="O34">
         <v>-0</v>
       </c>
       <c r="P34">
-        <v>-16.87096888163265</v>
+        <v>-17.52130528163265</v>
       </c>
       <c r="Q34">
-        <v>-16.32096888163265</v>
+        <v>-16.97130528163265</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1398742300084062</v>
+        <v>0.1412783229936062</v>
       </c>
       <c r="T34">
-        <v>1.83368184313607</v>
+        <v>1.861050228854519</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1893152873635547</v>
+        <v>0.1835784604737499</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1724704764057162</v>
+        <v>0.1743704764057162</v>
       </c>
       <c r="C35">
-        <v>72.13698473355841</v>
+        <v>67.65512963719578</v>
       </c>
       <c r="D35">
-        <v>116.6509847335584</v>
+        <v>114.9271296371958</v>
       </c>
       <c r="E35">
-        <v>82.61399999999999</v>
+        <v>85.37199999999999</v>
       </c>
       <c r="F35">
-        <v>91.014</v>
+        <v>93.77199999999999</v>
       </c>
       <c r="G35">
         <v>46.5</v>
@@ -4145,28 +4145,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M35">
-        <v>21.4611012</v>
+        <v>22.1114376</v>
       </c>
       <c r="N35">
-        <v>-17.52130528163265</v>
+        <v>-18.17164168163265</v>
       </c>
       <c r="O35">
         <v>-0</v>
       </c>
       <c r="P35">
-        <v>-17.52130528163265</v>
+        <v>-18.17164168163265</v>
       </c>
       <c r="Q35">
-        <v>-16.97130528163265</v>
+        <v>-17.62164168163265</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1412783229936062</v>
+        <v>0.1427249642510851</v>
       </c>
       <c r="T35">
-        <v>1.861050228854519</v>
+        <v>1.889247959594739</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1835784604737499</v>
+        <v>0.1781790939892279</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1743704764057162</v>
+        <v>0.1762704764057162</v>
       </c>
       <c r="C36">
-        <v>67.65512963719578</v>
+        <v>63.22348244645785</v>
       </c>
       <c r="D36">
-        <v>114.9271296371958</v>
+        <v>113.2534824464578</v>
       </c>
       <c r="E36">
-        <v>85.37199999999999</v>
+        <v>88.12999999999998</v>
       </c>
       <c r="F36">
-        <v>93.77199999999999</v>
+        <v>96.52999999999999</v>
       </c>
       <c r="G36">
         <v>46.5</v>
@@ -4227,28 +4227,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M36">
-        <v>22.1114376</v>
+        <v>22.761774</v>
       </c>
       <c r="N36">
-        <v>-18.17164168163265</v>
+        <v>-18.82197808163265</v>
       </c>
       <c r="O36">
         <v>-0</v>
       </c>
       <c r="P36">
-        <v>-18.17164168163265</v>
+        <v>-18.82197808163265</v>
       </c>
       <c r="Q36">
-        <v>-17.62164168163265</v>
+        <v>-18.27197808163265</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1427249642510851</v>
+        <v>0.1442161175472557</v>
       </c>
       <c r="T36">
-        <v>1.889247959594739</v>
+        <v>1.918313312819274</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1781790939892279</v>
+        <v>0.1730882627323929</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1762704764057162</v>
+        <v>0.1781704764057162</v>
       </c>
       <c r="C37">
-        <v>63.22348244645785</v>
+        <v>58.83988116064889</v>
       </c>
       <c r="D37">
-        <v>113.2534824464578</v>
+        <v>111.6278811606489</v>
       </c>
       <c r="E37">
-        <v>88.12999999999998</v>
+        <v>90.88799999999999</v>
       </c>
       <c r="F37">
-        <v>96.52999999999999</v>
+        <v>99.288</v>
       </c>
       <c r="G37">
         <v>46.5</v>
@@ -4309,28 +4309,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M37">
-        <v>22.761774</v>
+        <v>23.4121104</v>
       </c>
       <c r="N37">
-        <v>-18.82197808163265</v>
+        <v>-19.47231448163265</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>-18.82197808163265</v>
+        <v>-19.47231448163265</v>
       </c>
       <c r="Q37">
-        <v>-18.27197808163265</v>
+        <v>-18.92231448163265</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1442161175472557</v>
+        <v>0.1457538693839315</v>
       </c>
       <c r="T37">
-        <v>1.918313312819274</v>
+        <v>1.948286958332075</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1730882627323929</v>
+        <v>0.1682802554342708</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1781704764057162</v>
+        <v>0.1800704764057162</v>
       </c>
       <c r="C38">
-        <v>58.8398811606489</v>
+        <v>54.50228615299908</v>
       </c>
       <c r="D38">
-        <v>111.6278811606489</v>
+        <v>110.0482861529991</v>
       </c>
       <c r="E38">
-        <v>90.88799999999998</v>
+        <v>93.64599999999997</v>
       </c>
       <c r="F38">
-        <v>99.28799999999998</v>
+        <v>102.046</v>
       </c>
       <c r="G38">
         <v>46.5</v>
@@ -4391,28 +4391,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M38">
-        <v>23.4121104</v>
+        <v>24.0624468</v>
       </c>
       <c r="N38">
-        <v>-19.47231448163265</v>
+        <v>-20.12265088163265</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>-19.47231448163265</v>
+        <v>-20.12265088163265</v>
       </c>
       <c r="Q38">
-        <v>-18.92231448163265</v>
+        <v>-19.57265088163265</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1457538693839315</v>
+        <v>0.1473404387392321</v>
       </c>
       <c r="T38">
-        <v>1.948286958332075</v>
+        <v>1.97921214814687</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1682802554342708</v>
+        <v>0.1637321404225338</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1800704764057162</v>
+        <v>0.1819704764057162</v>
       </c>
       <c r="C39">
-        <v>54.50228615299908</v>
+        <v>50.20877163318708</v>
       </c>
       <c r="D39">
-        <v>110.0482861529991</v>
+        <v>108.5127716331871</v>
       </c>
       <c r="E39">
-        <v>93.64599999999997</v>
+        <v>96.40399999999998</v>
       </c>
       <c r="F39">
-        <v>102.046</v>
+        <v>104.804</v>
       </c>
       <c r="G39">
         <v>46.5</v>
@@ -4473,28 +4473,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M39">
-        <v>24.0624468</v>
+        <v>24.7127832</v>
       </c>
       <c r="N39">
-        <v>-20.12265088163265</v>
+        <v>-20.77298728163265</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-20.12265088163265</v>
+        <v>-20.77298728163265</v>
       </c>
       <c r="Q39">
-        <v>-19.57265088163265</v>
+        <v>-20.22298728163265</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1473404387392321</v>
+        <v>0.1489781877511551</v>
       </c>
       <c r="T39">
-        <v>1.97921214814687</v>
+        <v>2.011134924729883</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1637321404225338</v>
+        <v>0.1594233998850987</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1819704764057162</v>
+        <v>0.1838704764057162</v>
       </c>
       <c r="C40">
-        <v>50.20877163318708</v>
+        <v>45.95751781477324</v>
       </c>
       <c r="D40">
-        <v>108.5127716331871</v>
+        <v>107.0195178147732</v>
       </c>
       <c r="E40">
-        <v>96.40399999999998</v>
+        <v>99.16199999999998</v>
       </c>
       <c r="F40">
-        <v>104.804</v>
+        <v>107.562</v>
       </c>
       <c r="G40">
         <v>46.5</v>
@@ -4555,28 +4555,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M40">
-        <v>24.7127832</v>
+        <v>25.3631196</v>
       </c>
       <c r="N40">
-        <v>-20.77298728163265</v>
+        <v>-21.42332368163265</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-20.77298728163265</v>
+        <v>-21.42332368163265</v>
       </c>
       <c r="Q40">
-        <v>-20.22298728163265</v>
+        <v>-20.87332368163265</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1489781877511551</v>
+        <v>0.1506696334519937</v>
       </c>
       <c r="T40">
-        <v>2.011134924729883</v>
+        <v>2.044104349725455</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1594233998850987</v>
+        <v>0.1553356204008653</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1838704764057162</v>
+        <v>0.1857704764057162</v>
       </c>
       <c r="C41">
-        <v>45.95751781477324</v>
+        <v>41.74680372056179</v>
       </c>
       <c r="D41">
-        <v>107.0195178147732</v>
+        <v>105.5668037205618</v>
       </c>
       <c r="E41">
-        <v>99.16199999999998</v>
+        <v>101.92</v>
       </c>
       <c r="F41">
-        <v>107.562</v>
+        <v>110.32</v>
       </c>
       <c r="G41">
         <v>46.5</v>
@@ -4637,28 +4637,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M41">
-        <v>25.3631196</v>
+        <v>26.013456</v>
       </c>
       <c r="N41">
-        <v>-21.42332368163265</v>
+        <v>-22.07366008163265</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-21.42332368163265</v>
+        <v>-22.07366008163265</v>
       </c>
       <c r="Q41">
-        <v>-20.87332368163265</v>
+        <v>-21.52366008163265</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1506696334519937</v>
+        <v>0.1524174606761936</v>
       </c>
       <c r="T41">
-        <v>2.044104349725455</v>
+        <v>2.078172755554213</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1553356204008653</v>
+        <v>0.1514522298908437</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1857704764057162</v>
+        <v>0.1876704764057162</v>
       </c>
       <c r="C42">
-        <v>41.74680372056179</v>
+        <v>37.57500056608824</v>
       </c>
       <c r="D42">
-        <v>105.5668037205618</v>
+        <v>104.1530005660882</v>
       </c>
       <c r="E42">
-        <v>101.92</v>
+        <v>104.678</v>
       </c>
       <c r="F42">
-        <v>110.32</v>
+        <v>113.078</v>
       </c>
       <c r="G42">
         <v>46.5</v>
@@ -4719,28 +4719,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M42">
-        <v>26.013456</v>
+        <v>26.6637924</v>
       </c>
       <c r="N42">
-        <v>-22.07366008163265</v>
+        <v>-22.72399648163265</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-22.07366008163265</v>
+        <v>-22.72399648163265</v>
       </c>
       <c r="Q42">
-        <v>-21.52366008163265</v>
+        <v>-22.17399648163265</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1524174606761936</v>
+        <v>0.1542245362808749</v>
       </c>
       <c r="T42">
-        <v>2.078172755554213</v>
+        <v>2.113396022597505</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1514522298908437</v>
+        <v>0.1477582730642378</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1876704764057162</v>
+        <v>0.1895704764057162</v>
       </c>
       <c r="C43">
-        <v>37.57500056608824</v>
+        <v>33.44056566774982</v>
       </c>
       <c r="D43">
-        <v>104.1530005660882</v>
+        <v>102.7765656677498</v>
       </c>
       <c r="E43">
-        <v>104.678</v>
+        <v>107.436</v>
       </c>
       <c r="F43">
-        <v>113.078</v>
+        <v>115.836</v>
       </c>
       <c r="G43">
         <v>46.5</v>
@@ -4801,28 +4801,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M43">
-        <v>26.6637924</v>
+        <v>27.3141288</v>
       </c>
       <c r="N43">
-        <v>-22.72399648163265</v>
+        <v>-23.37433288163265</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-22.72399648163265</v>
+        <v>-23.37433288163265</v>
       </c>
       <c r="Q43">
-        <v>-22.17399648163265</v>
+        <v>-22.82433288163265</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1542245362808749</v>
+        <v>0.1560939248374417</v>
       </c>
       <c r="T43">
-        <v>2.113396022597505</v>
+        <v>2.149833885056082</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1477582730642378</v>
+        <v>0.1442402189436607</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1895704764057162</v>
+        <v>0.1914704764057162</v>
       </c>
       <c r="C44">
-        <v>33.44056566774985</v>
+        <v>29.342036827679</v>
       </c>
       <c r="D44">
-        <v>102.7765656677498</v>
+        <v>101.436036827679</v>
       </c>
       <c r="E44">
-        <v>107.436</v>
+        <v>110.194</v>
       </c>
       <c r="F44">
-        <v>115.836</v>
+        <v>118.594</v>
       </c>
       <c r="G44">
         <v>46.5</v>
@@ -4883,28 +4883,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M44">
-        <v>27.3141288</v>
+        <v>27.9644652</v>
       </c>
       <c r="N44">
-        <v>-23.37433288163265</v>
+        <v>-24.02466928163265</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-23.37433288163265</v>
+        <v>-24.02466928163265</v>
       </c>
       <c r="Q44">
-        <v>-22.82433288163265</v>
+        <v>-23.47466928163265</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1560939248374417</v>
+        <v>0.1580289059749407</v>
       </c>
       <c r="T44">
-        <v>2.149833885056082</v>
+        <v>2.187550269004435</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1442402189436607</v>
+        <v>0.1408857952472965</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1914704764057162</v>
+        <v>0.1933704764057162</v>
       </c>
       <c r="C45">
-        <v>29.342036827679</v>
+        <v>25.27802715239187</v>
       </c>
       <c r="D45">
-        <v>101.436036827679</v>
+        <v>100.1300271523919</v>
       </c>
       <c r="E45">
-        <v>110.194</v>
+        <v>112.952</v>
       </c>
       <c r="F45">
-        <v>118.594</v>
+        <v>121.352</v>
       </c>
       <c r="G45">
         <v>46.5</v>
@@ -4965,28 +4965,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M45">
-        <v>27.9644652</v>
+        <v>28.6148016</v>
       </c>
       <c r="N45">
-        <v>-24.02466928163265</v>
+        <v>-24.67500568163265</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-24.02466928163265</v>
+        <v>-24.67500568163265</v>
       </c>
       <c r="Q45">
-        <v>-23.47466928163265</v>
+        <v>-24.12500568163265</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1580289059749407</v>
+        <v>0.160032993581636</v>
       </c>
       <c r="T45">
-        <v>2.187550269004435</v>
+        <v>2.226613666665228</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1408857952472965</v>
+        <v>0.1376838453553125</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1933704764057162</v>
+        <v>0.1952704764057162</v>
       </c>
       <c r="C46">
-        <v>25.27802715239187</v>
+        <v>21.24722026661502</v>
       </c>
       <c r="D46">
-        <v>100.1300271523919</v>
+        <v>98.85722026661499</v>
       </c>
       <c r="E46">
-        <v>112.952</v>
+        <v>115.71</v>
       </c>
       <c r="F46">
-        <v>121.352</v>
+        <v>124.11</v>
       </c>
       <c r="G46">
         <v>46.5</v>
@@ -5047,28 +5047,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M46">
-        <v>28.6148016</v>
+        <v>29.265138</v>
       </c>
       <c r="N46">
-        <v>-24.67500568163265</v>
+        <v>-25.32534208163265</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-24.67500568163265</v>
+        <v>-25.32534208163265</v>
       </c>
       <c r="Q46">
-        <v>-24.12500568163265</v>
+        <v>-24.77534208163265</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.160032993581636</v>
+        <v>0.1621099571013022</v>
       </c>
       <c r="T46">
-        <v>2.226613666665228</v>
+        <v>2.267097551513687</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1376838453553125</v>
+        <v>0.1346242043474167</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1952704764057162</v>
+        <v>0.1971704764057162</v>
       </c>
       <c r="C47">
-        <v>21.24722026661502</v>
+        <v>17.24836588756729</v>
       </c>
       <c r="D47">
-        <v>98.85722026661499</v>
+        <v>97.61636588756728</v>
       </c>
       <c r="E47">
-        <v>115.71</v>
+        <v>118.468</v>
       </c>
       <c r="F47">
-        <v>124.11</v>
+        <v>126.868</v>
       </c>
       <c r="G47">
         <v>46.5</v>
@@ -5129,28 +5129,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M47">
-        <v>29.265138</v>
+        <v>29.9154744</v>
       </c>
       <c r="N47">
-        <v>-25.32534208163265</v>
+        <v>-25.97567848163265</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-25.32534208163265</v>
+        <v>-25.97567848163265</v>
       </c>
       <c r="Q47">
-        <v>-24.77534208163265</v>
+        <v>-25.42567848163265</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1621099571013022</v>
+        <v>0.1642638451957707</v>
       </c>
       <c r="T47">
-        <v>2.267097551513687</v>
+        <v>2.309080839504681</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1346242043474167</v>
+        <v>0.1316975912094294</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1971704764057162</v>
+        <v>0.1990704764057162</v>
       </c>
       <c r="C48">
-        <v>17.24836588756729</v>
+        <v>13.28027572842001</v>
       </c>
       <c r="D48">
-        <v>97.61636588756728</v>
+        <v>96.40627572842</v>
       </c>
       <c r="E48">
-        <v>118.468</v>
+        <v>121.226</v>
       </c>
       <c r="F48">
-        <v>126.868</v>
+        <v>129.626</v>
       </c>
       <c r="G48">
         <v>46.5</v>
@@ -5211,28 +5211,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M48">
-        <v>29.9154744</v>
+        <v>30.56581079999999</v>
       </c>
       <c r="N48">
-        <v>-25.97567848163265</v>
+        <v>-26.62601488163265</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-25.97567848163265</v>
+        <v>-26.62601488163265</v>
       </c>
       <c r="Q48">
-        <v>-25.42567848163265</v>
+        <v>-26.07601488163264</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1642638451957707</v>
+        <v>0.1664990120862569</v>
       </c>
       <c r="T48">
-        <v>2.309080839504681</v>
+        <v>2.352648402514203</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1316975912094294</v>
+        <v>0.1288955148007181</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1990704764057162</v>
+        <v>0.2009704764057162</v>
       </c>
       <c r="C49">
-        <v>13.28027572842001</v>
+        <v>9.341819702719164</v>
       </c>
       <c r="D49">
-        <v>96.40627572842</v>
+        <v>95.22581970271916</v>
       </c>
       <c r="E49">
-        <v>121.226</v>
+        <v>123.984</v>
       </c>
       <c r="F49">
-        <v>129.626</v>
+        <v>132.384</v>
       </c>
       <c r="G49">
         <v>46.5</v>
@@ -5293,28 +5293,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M49">
-        <v>30.56581079999999</v>
+        <v>31.2161472</v>
       </c>
       <c r="N49">
-        <v>-26.62601488163265</v>
+        <v>-27.27635128163265</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-26.62601488163265</v>
+        <v>-27.27635128163265</v>
       </c>
       <c r="Q49">
-        <v>-26.07601488163264</v>
+        <v>-26.72635128163265</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1664990120862569</v>
+        <v>0.1688201469340696</v>
       </c>
       <c r="T49">
-        <v>2.352648402514203</v>
+        <v>2.397891641024092</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1288955148007181</v>
+        <v>0.1262101915757031</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2009704764057162</v>
+        <v>0.2028704764057162</v>
       </c>
       <c r="C50">
-        <v>9.341819702719164</v>
+        <v>5.431922404287207</v>
       </c>
       <c r="D50">
-        <v>95.22581970271916</v>
+        <v>94.07392240428717</v>
       </c>
       <c r="E50">
-        <v>123.984</v>
+        <v>126.742</v>
       </c>
       <c r="F50">
-        <v>132.384</v>
+        <v>135.142</v>
       </c>
       <c r="G50">
         <v>46.5</v>
@@ -5375,28 +5375,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M50">
-        <v>31.2161472</v>
+        <v>31.8664836</v>
       </c>
       <c r="N50">
-        <v>-27.27635128163265</v>
+        <v>-27.92668768163265</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-27.27635128163265</v>
+        <v>-27.92668768163265</v>
       </c>
       <c r="Q50">
-        <v>-26.72635128163265</v>
+        <v>-27.37668768163265</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1688201469340696</v>
+        <v>0.1712323066778749</v>
       </c>
       <c r="T50">
-        <v>2.397891641024092</v>
+        <v>2.444909124181427</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1262101915757031</v>
+        <v>0.1236344733802807</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2028704764057162</v>
+        <v>0.2047704764057162</v>
       </c>
       <c r="C51">
-        <v>5.431922404287207</v>
+        <v>1.54955983955557</v>
       </c>
       <c r="D51">
-        <v>94.07392240428717</v>
+        <v>92.94955983955553</v>
       </c>
       <c r="E51">
-        <v>126.742</v>
+        <v>129.5</v>
       </c>
       <c r="F51">
-        <v>135.142</v>
+        <v>137.9</v>
       </c>
       <c r="G51">
         <v>46.5</v>
@@ -5457,28 +5457,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M51">
-        <v>31.8664836</v>
+        <v>32.51682</v>
       </c>
       <c r="N51">
-        <v>-27.92668768163265</v>
+        <v>-28.57702408163265</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-27.92668768163265</v>
+        <v>-28.57702408163265</v>
       </c>
       <c r="Q51">
-        <v>-27.37668768163265</v>
+        <v>-28.02702408163265</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1712323066778749</v>
+        <v>0.1737409528114324</v>
       </c>
       <c r="T51">
-        <v>2.444909124181427</v>
+        <v>2.493807306665055</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1236344733802807</v>
+        <v>0.121161783912675</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2047704764057162</v>
+        <v>0.2066704764057162</v>
       </c>
       <c r="C52">
-        <v>1.54955983955557</v>
+        <v>-2.306243608541166</v>
       </c>
       <c r="D52">
-        <v>92.94955983955553</v>
+        <v>91.85175639145884</v>
       </c>
       <c r="E52">
-        <v>129.5</v>
+        <v>132.258</v>
       </c>
       <c r="F52">
-        <v>137.9</v>
+        <v>140.658</v>
       </c>
       <c r="G52">
         <v>46.5</v>
@@ -5539,28 +5539,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M52">
-        <v>32.51682</v>
+        <v>33.1671564</v>
       </c>
       <c r="N52">
-        <v>-28.57702408163265</v>
+        <v>-29.22736048163265</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-28.57702408163265</v>
+        <v>-29.22736048163265</v>
       </c>
       <c r="Q52">
-        <v>-28.02702408163265</v>
+        <v>-28.67736048163265</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1737409528114324</v>
+        <v>0.1763519926647269</v>
       </c>
       <c r="T52">
-        <v>2.493807306665055</v>
+        <v>2.544701333331689</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.121161783912675</v>
+        <v>0.1187860626594853</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2066704764057162</v>
+        <v>0.2085704764057162</v>
       </c>
       <c r="C53">
-        <v>-2.306243608541166</v>
+        <v>-6.136418004030247</v>
       </c>
       <c r="D53">
-        <v>91.85175639145884</v>
+        <v>90.77958199596972</v>
       </c>
       <c r="E53">
-        <v>132.258</v>
+        <v>135.016</v>
       </c>
       <c r="F53">
-        <v>140.658</v>
+        <v>143.416</v>
       </c>
       <c r="G53">
         <v>46.5</v>
@@ -5621,28 +5621,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M53">
-        <v>33.1671564</v>
+        <v>33.8174928</v>
       </c>
       <c r="N53">
-        <v>-29.22736048163265</v>
+        <v>-29.87769688163265</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-29.22736048163265</v>
+        <v>-29.87769688163265</v>
       </c>
       <c r="Q53">
-        <v>-28.67736048163265</v>
+        <v>-29.32769688163265</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1763519926647269</v>
+        <v>0.1790718258452421</v>
       </c>
       <c r="T53">
-        <v>2.544701333331689</v>
+        <v>2.597715944442766</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1187860626594853</v>
+        <v>0.116501715300649</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2085704764057162</v>
+        <v>0.2104704764057162</v>
       </c>
       <c r="C54">
-        <v>-6.136418004030247</v>
+        <v>-9.941850485900204</v>
       </c>
       <c r="D54">
-        <v>90.77958199596972</v>
+        <v>89.73214951409979</v>
       </c>
       <c r="E54">
-        <v>135.016</v>
+        <v>137.774</v>
       </c>
       <c r="F54">
-        <v>143.416</v>
+        <v>146.174</v>
       </c>
       <c r="G54">
         <v>46.5</v>
@@ -5703,28 +5703,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M54">
-        <v>33.8174928</v>
+        <v>34.4678292</v>
       </c>
       <c r="N54">
-        <v>-29.87769688163265</v>
+        <v>-30.52803328163265</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-29.87769688163265</v>
+        <v>-30.52803328163265</v>
       </c>
       <c r="Q54">
-        <v>-29.32769688163265</v>
+        <v>-29.97803328163265</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1790718258452421</v>
+        <v>0.1819073966079068</v>
       </c>
       <c r="T54">
-        <v>2.597715944442766</v>
+        <v>2.652986496452187</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.116501715300649</v>
+        <v>0.1143035697289387</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2104704764057162</v>
+        <v>0.2123704764057162</v>
       </c>
       <c r="C55">
-        <v>-9.941850485900204</v>
+        <v>-13.72338771624061</v>
       </c>
       <c r="D55">
-        <v>89.73214951409979</v>
+        <v>88.70861228375938</v>
       </c>
       <c r="E55">
-        <v>137.774</v>
+        <v>140.532</v>
       </c>
       <c r="F55">
-        <v>146.174</v>
+        <v>148.932</v>
       </c>
       <c r="G55">
         <v>46.5</v>
@@ -5785,28 +5785,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M55">
-        <v>34.4678292</v>
+        <v>35.1181656</v>
       </c>
       <c r="N55">
-        <v>-30.52803328163265</v>
+        <v>-31.17836968163265</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-30.52803328163265</v>
+        <v>-31.17836968163265</v>
       </c>
       <c r="Q55">
-        <v>-29.97803328163265</v>
+        <v>-30.62836968163265</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1819073966079068</v>
+        <v>0.1848662530559048</v>
       </c>
       <c r="T55">
-        <v>2.652986496452187</v>
+        <v>2.710660115940278</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1143035697289387</v>
+        <v>0.1121868369561806</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2123704764057162</v>
+        <v>0.2142704764057162</v>
       </c>
       <c r="C56">
-        <v>-13.72338771624061</v>
+        <v>-17.48183816272268</v>
       </c>
       <c r="D56">
-        <v>88.70861228375938</v>
+        <v>87.70816183727732</v>
       </c>
       <c r="E56">
-        <v>140.532</v>
+        <v>143.29</v>
       </c>
       <c r="F56">
-        <v>148.932</v>
+        <v>151.69</v>
       </c>
       <c r="G56">
         <v>46.5</v>
@@ -5867,28 +5867,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M56">
-        <v>35.1181656</v>
+        <v>35.768502</v>
       </c>
       <c r="N56">
-        <v>-31.17836968163265</v>
+        <v>-31.82870608163265</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-31.17836968163265</v>
+        <v>-31.82870608163265</v>
       </c>
       <c r="Q56">
-        <v>-30.62836968163265</v>
+        <v>-31.27870608163265</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1848662530559048</v>
+        <v>0.1879566142349249</v>
       </c>
       <c r="T56">
-        <v>2.710660115940278</v>
+        <v>2.770897007405617</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1121868369561806</v>
+        <v>0.11014707628425</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2142704764057162</v>
+        <v>0.2161704764057162</v>
       </c>
       <c r="C57">
-        <v>-17.48183816272268</v>
+        <v>-21.21797422835169</v>
       </c>
       <c r="D57">
-        <v>87.70816183727732</v>
+        <v>86.7300257716483</v>
       </c>
       <c r="E57">
-        <v>143.29</v>
+        <v>146.048</v>
       </c>
       <c r="F57">
-        <v>151.69</v>
+        <v>154.448</v>
       </c>
       <c r="G57">
         <v>46.5</v>
@@ -5949,28 +5949,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M57">
-        <v>35.768502</v>
+        <v>36.4188384</v>
       </c>
       <c r="N57">
-        <v>-31.82870608163265</v>
+        <v>-32.47904248163265</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-31.82870608163265</v>
+        <v>-32.47904248163265</v>
       </c>
       <c r="Q57">
-        <v>-31.27870608163265</v>
+        <v>-31.92904248163265</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1879566142349249</v>
+        <v>0.1911874463766277</v>
       </c>
       <c r="T57">
-        <v>2.770897007405617</v>
+        <v>2.833871939392109</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.11014707628425</v>
+        <v>0.1081801642077455</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2161704764057162</v>
+        <v>0.2180704764057162</v>
       </c>
       <c r="C58">
-        <v>-21.21797422835169</v>
+        <v>-24.93253424028339</v>
       </c>
       <c r="D58">
-        <v>86.7300257716483</v>
+        <v>85.77346575971661</v>
       </c>
       <c r="E58">
-        <v>146.048</v>
+        <v>148.806</v>
       </c>
       <c r="F58">
-        <v>154.448</v>
+        <v>157.206</v>
       </c>
       <c r="G58">
         <v>46.5</v>
@@ -6031,28 +6031,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M58">
-        <v>36.4188384</v>
+        <v>37.0691748</v>
       </c>
       <c r="N58">
-        <v>-32.47904248163265</v>
+        <v>-33.12937888163265</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-32.47904248163265</v>
+        <v>-33.12937888163265</v>
       </c>
       <c r="Q58">
-        <v>-31.92904248163265</v>
+        <v>-32.57937888163266</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1911874463766277</v>
+        <v>0.1945685497807354</v>
       </c>
       <c r="T58">
-        <v>2.833871939392109</v>
+        <v>2.899775937982624</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1081801642077455</v>
+        <v>0.1062822665900657</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2180704764057162</v>
+        <v>0.2199704764057162</v>
       </c>
       <c r="C59">
-        <v>-24.93253424028339</v>
+        <v>-28.62622430846602</v>
       </c>
       <c r="D59">
-        <v>85.77346575971661</v>
+        <v>84.83777569153399</v>
       </c>
       <c r="E59">
-        <v>148.806</v>
+        <v>151.564</v>
       </c>
       <c r="F59">
-        <v>157.206</v>
+        <v>159.964</v>
       </c>
       <c r="G59">
         <v>46.5</v>
@@ -6113,28 +6113,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M59">
-        <v>37.0691748</v>
+        <v>37.7195112</v>
       </c>
       <c r="N59">
-        <v>-33.12937888163265</v>
+        <v>-33.77971528163265</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-33.12937888163265</v>
+        <v>-33.77971528163265</v>
       </c>
       <c r="Q59">
-        <v>-32.57937888163266</v>
+        <v>-33.22971528163266</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1945685497807354</v>
+        <v>0.1981106581088481</v>
       </c>
       <c r="T59">
-        <v>2.899775937982624</v>
+        <v>2.968818222220305</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1062822665900657</v>
+        <v>0.1044498137178231</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2199704764057162</v>
+        <v>0.2218704764057162</v>
       </c>
       <c r="C60">
-        <v>-28.62622430846594</v>
+        <v>-32.29972006394104</v>
       </c>
       <c r="D60">
-        <v>84.83777569153402</v>
+        <v>83.92227993605891</v>
       </c>
       <c r="E60">
-        <v>151.564</v>
+        <v>154.3219999999999</v>
       </c>
       <c r="F60">
-        <v>159.964</v>
+        <v>162.722</v>
       </c>
       <c r="G60">
         <v>46.5</v>
@@ -6195,28 +6195,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M60">
-        <v>37.71951119999999</v>
+        <v>38.36984759999999</v>
       </c>
       <c r="N60">
-        <v>-33.77971528163265</v>
+        <v>-34.43005168163265</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-33.77971528163265</v>
+        <v>-34.43005168163265</v>
       </c>
       <c r="Q60">
-        <v>-33.22971528163265</v>
+        <v>-33.88005168163265</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.198110658108848</v>
+        <v>0.2018255522090638</v>
       </c>
       <c r="T60">
-        <v>2.968818222220304</v>
+        <v>3.041228422762262</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1044498137178232</v>
+        <v>0.1026794778920974</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2218704764057162</v>
+        <v>0.2237704764057162</v>
       </c>
       <c r="C61">
-        <v>-32.29972006394104</v>
+        <v>-35.95366828579674</v>
       </c>
       <c r="D61">
-        <v>83.92227993605891</v>
+        <v>83.02633171420322</v>
       </c>
       <c r="E61">
-        <v>154.3219999999999</v>
+        <v>157.08</v>
       </c>
       <c r="F61">
-        <v>162.722</v>
+        <v>165.48</v>
       </c>
       <c r="G61">
         <v>46.5</v>
@@ -6277,28 +6277,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M61">
-        <v>38.36984759999999</v>
+        <v>39.02018399999999</v>
       </c>
       <c r="N61">
-        <v>-34.43005168163265</v>
+        <v>-35.08038808163265</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-34.43005168163265</v>
+        <v>-35.08038808163265</v>
       </c>
       <c r="Q61">
-        <v>-33.88005168163265</v>
+        <v>-34.53038808163265</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2018255522090638</v>
+        <v>0.2057261910142905</v>
       </c>
       <c r="T61">
-        <v>3.041228422762262</v>
+        <v>3.117259133331319</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1026794778920974</v>
+        <v>0.1009681532605624</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2237704764057162</v>
+        <v>0.2256704764057162</v>
       </c>
       <c r="C62">
-        <v>-35.95366828579674</v>
+        <v>-39.5886884250061</v>
       </c>
       <c r="D62">
-        <v>83.02633171420322</v>
+        <v>82.14931157499389</v>
       </c>
       <c r="E62">
-        <v>157.08</v>
+        <v>159.838</v>
       </c>
       <c r="F62">
-        <v>165.48</v>
+        <v>168.238</v>
       </c>
       <c r="G62">
         <v>46.5</v>
@@ -6359,28 +6359,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M62">
-        <v>39.02018399999999</v>
+        <v>39.67052039999999</v>
       </c>
       <c r="N62">
-        <v>-35.08038808163265</v>
+        <v>-35.73072448163265</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-35.08038808163265</v>
+        <v>-35.73072448163265</v>
       </c>
       <c r="Q62">
-        <v>-34.53038808163265</v>
+        <v>-35.18072448163265</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2057261910142905</v>
+        <v>0.2098268625787594</v>
       </c>
       <c r="T62">
-        <v>3.117259133331319</v>
+        <v>3.197188854698789</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1009681532605624</v>
+        <v>0.09931293763334004</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2256704764057162</v>
+        <v>0.2275704764057162</v>
       </c>
       <c r="C63">
-        <v>-39.5886884250061</v>
+        <v>-43.20537403269577</v>
       </c>
       <c r="D63">
-        <v>82.14931157499389</v>
+        <v>81.29062596730421</v>
       </c>
       <c r="E63">
-        <v>159.838</v>
+        <v>162.596</v>
       </c>
       <c r="F63">
-        <v>168.238</v>
+        <v>170.996</v>
       </c>
       <c r="G63">
         <v>46.5</v>
@@ -6441,28 +6441,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M63">
-        <v>39.67052039999999</v>
+        <v>40.32085679999999</v>
       </c>
       <c r="N63">
-        <v>-35.73072448163265</v>
+        <v>-36.38106088163265</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-35.73072448163265</v>
+        <v>-36.38106088163265</v>
       </c>
       <c r="Q63">
-        <v>-35.18072448163265</v>
+        <v>-35.83106088163265</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2098268625787594</v>
+        <v>0.214143358962411</v>
       </c>
       <c r="T63">
-        <v>3.197188854698789</v>
+        <v>3.281325403506652</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.09931293763334004</v>
+        <v>0.09771111605860883</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2275704764057162</v>
+        <v>0.2294704764057162</v>
       </c>
       <c r="C64">
-        <v>-43.20537403269577</v>
+        <v>-46.8042940997658</v>
       </c>
       <c r="D64">
-        <v>81.29062596730421</v>
+        <v>80.44970590023416</v>
       </c>
       <c r="E64">
-        <v>162.596</v>
+        <v>165.354</v>
       </c>
       <c r="F64">
-        <v>170.996</v>
+        <v>173.754</v>
       </c>
       <c r="G64">
         <v>46.5</v>
@@ -6523,28 +6523,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M64">
-        <v>40.32085679999999</v>
+        <v>40.97119319999999</v>
       </c>
       <c r="N64">
-        <v>-36.38106088163265</v>
+        <v>-37.03139728163265</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-36.38106088163265</v>
+        <v>-37.03139728163265</v>
       </c>
       <c r="Q64">
-        <v>-35.83106088163265</v>
+        <v>-36.48139728163265</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.214143358962411</v>
+        <v>0.2186931794749086</v>
       </c>
       <c r="T64">
-        <v>3.281325403506652</v>
+        <v>3.370009873871696</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.09771111605860883</v>
+        <v>0.09616014596244038</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2294704764057162</v>
+        <v>0.2313704764057162</v>
       </c>
       <c r="C65">
-        <v>-46.8042940997658</v>
+        <v>-50.38599431421295</v>
       </c>
       <c r="D65">
-        <v>80.44970590023416</v>
+        <v>79.62600568578702</v>
       </c>
       <c r="E65">
-        <v>165.354</v>
+        <v>168.112</v>
       </c>
       <c r="F65">
-        <v>173.754</v>
+        <v>176.512</v>
       </c>
       <c r="G65">
         <v>46.5</v>
@@ -6605,28 +6605,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M65">
-        <v>40.97119319999999</v>
+        <v>41.6215296</v>
       </c>
       <c r="N65">
-        <v>-37.03139728163265</v>
+        <v>-37.68173368163265</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-37.03139728163265</v>
+        <v>-37.68173368163265</v>
       </c>
       <c r="Q65">
-        <v>-36.48139728163265</v>
+        <v>-37.13173368163265</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2186931794749086</v>
+        <v>0.2234957677936561</v>
       </c>
       <c r="T65">
-        <v>3.370009873871696</v>
+        <v>3.463621259257021</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.09616014596244038</v>
+        <v>0.09465764368177731</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2313704764057162</v>
+        <v>0.2332704764057162</v>
       </c>
       <c r="C66">
-        <v>-50.38599431421295</v>
+        <v>-53.95099824199718</v>
       </c>
       <c r="D66">
-        <v>79.62600568578702</v>
+        <v>78.8190017580028</v>
       </c>
       <c r="E66">
-        <v>168.112</v>
+        <v>170.87</v>
       </c>
       <c r="F66">
-        <v>176.512</v>
+        <v>179.27</v>
       </c>
       <c r="G66">
         <v>46.5</v>
@@ -6687,28 +6687,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M66">
-        <v>41.6215296</v>
+        <v>42.271866</v>
       </c>
       <c r="N66">
-        <v>-37.68173368163265</v>
+        <v>-38.33207008163265</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-37.68173368163265</v>
+        <v>-38.33207008163265</v>
       </c>
       <c r="Q66">
-        <v>-37.13173368163265</v>
+        <v>-37.78207008163265</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2234957677936561</v>
+        <v>0.2285727897306177</v>
       </c>
       <c r="T66">
-        <v>3.463621259257021</v>
+        <v>3.562581866664365</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.09465764368177731</v>
+        <v>0.09320137224051916</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2332704764057162</v>
+        <v>0.2351704764057162</v>
       </c>
       <c r="C67">
-        <v>-53.95099824199718</v>
+        <v>-57.4998084368206</v>
       </c>
       <c r="D67">
-        <v>78.8190017580028</v>
+        <v>78.02819156317939</v>
       </c>
       <c r="E67">
-        <v>170.87</v>
+        <v>173.628</v>
       </c>
       <c r="F67">
-        <v>179.27</v>
+        <v>182.028</v>
       </c>
       <c r="G67">
         <v>46.5</v>
@@ -6769,28 +6769,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M67">
-        <v>42.271866</v>
+        <v>42.9222024</v>
       </c>
       <c r="N67">
-        <v>-38.33207008163265</v>
+        <v>-38.98240648163266</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-38.33207008163265</v>
+        <v>-38.98240648163266</v>
       </c>
       <c r="Q67">
-        <v>-37.78207008163265</v>
+        <v>-38.43240648163266</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2285727897306177</v>
+        <v>0.2339484600168123</v>
       </c>
       <c r="T67">
-        <v>3.562581866664365</v>
+        <v>3.667363686272141</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.09320137224051916</v>
+        <v>0.09178923023687491</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2351704764057162</v>
+        <v>0.2370704764057162</v>
       </c>
       <c r="C68">
-        <v>-57.4998084368206</v>
+        <v>-61.03290748376166</v>
       </c>
       <c r="D68">
-        <v>78.02819156317939</v>
+        <v>77.25309251623831</v>
       </c>
       <c r="E68">
-        <v>173.628</v>
+        <v>176.386</v>
       </c>
       <c r="F68">
-        <v>182.028</v>
+        <v>184.786</v>
       </c>
       <c r="G68">
         <v>46.5</v>
@@ -6851,28 +6851,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M68">
-        <v>42.9222024</v>
+        <v>43.5725388</v>
       </c>
       <c r="N68">
-        <v>-38.98240648163266</v>
+        <v>-39.63274288163265</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-38.98240648163266</v>
+        <v>-39.63274288163265</v>
       </c>
       <c r="Q68">
-        <v>-38.43240648163266</v>
+        <v>-39.08274288163265</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2339484600168123</v>
+        <v>0.2396499285021703</v>
       </c>
       <c r="T68">
-        <v>3.667363686272141</v>
+        <v>3.778495919189479</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.09178923023687491</v>
+        <v>0.09041924172587679</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2370704764057162</v>
+        <v>0.2389704764057162</v>
       </c>
       <c r="C69">
-        <v>-61.03290748376166</v>
+        <v>-64.55075898131955</v>
       </c>
       <c r="D69">
-        <v>77.25309251623831</v>
+        <v>76.49324101868044</v>
       </c>
       <c r="E69">
-        <v>176.386</v>
+        <v>179.144</v>
       </c>
       <c r="F69">
-        <v>184.786</v>
+        <v>187.544</v>
       </c>
       <c r="G69">
         <v>46.5</v>
@@ -6933,28 +6933,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M69">
-        <v>43.5725388</v>
+        <v>44.2228752</v>
       </c>
       <c r="N69">
-        <v>-39.63274288163265</v>
+        <v>-40.28307928163265</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-39.63274288163265</v>
+        <v>-40.28307928163265</v>
       </c>
       <c r="Q69">
-        <v>-39.08274288163265</v>
+        <v>-39.73307928163266</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2396499285021703</v>
+        <v>0.2457077387678631</v>
       </c>
       <c r="T69">
-        <v>3.778495919189479</v>
+        <v>3.89657391666415</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.09041924172587679</v>
+        <v>0.08908954699461391</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2389704764057162</v>
+        <v>0.2408704764057162</v>
       </c>
       <c r="C70">
-        <v>-64.55075898131955</v>
+        <v>-68.05380846606687</v>
       </c>
       <c r="D70">
-        <v>76.49324101868044</v>
+        <v>75.74819153393312</v>
       </c>
       <c r="E70">
-        <v>179.144</v>
+        <v>181.902</v>
       </c>
       <c r="F70">
-        <v>187.544</v>
+        <v>190.302</v>
       </c>
       <c r="G70">
         <v>46.5</v>
@@ -7015,28 +7015,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M70">
-        <v>44.2228752</v>
+        <v>44.8732116</v>
       </c>
       <c r="N70">
-        <v>-40.28307928163265</v>
+        <v>-40.93341568163265</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-40.28307928163265</v>
+        <v>-40.93341568163265</v>
       </c>
       <c r="Q70">
-        <v>-39.73307928163266</v>
+        <v>-40.38341568163266</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2457077387678631</v>
+        <v>0.2521563755023103</v>
       </c>
       <c r="T70">
-        <v>3.89657391666415</v>
+        <v>4.022269849459768</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.08908954699461391</v>
+        <v>0.08779839413961954</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2408704764057162</v>
+        <v>0.2427704764057162</v>
       </c>
       <c r="C71">
-        <v>-68.05380846606687</v>
+        <v>-71.542484283787</v>
       </c>
       <c r="D71">
-        <v>75.74819153393312</v>
+        <v>75.01751571621297</v>
       </c>
       <c r="E71">
-        <v>181.902</v>
+        <v>184.66</v>
       </c>
       <c r="F71">
-        <v>190.302</v>
+        <v>193.06</v>
       </c>
       <c r="G71">
         <v>46.5</v>
@@ -7097,28 +7097,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M71">
-        <v>44.8732116</v>
+        <v>45.523548</v>
       </c>
       <c r="N71">
-        <v>-40.93341568163265</v>
+        <v>-41.58375208163265</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-40.93341568163265</v>
+        <v>-41.58375208163265</v>
       </c>
       <c r="Q71">
-        <v>-40.38341568163266</v>
+        <v>-41.03375208163266</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2521563755023103</v>
+        <v>0.2590349213523873</v>
       </c>
       <c r="T71">
-        <v>4.022269849459768</v>
+        <v>4.156345511108427</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.08779839413961954</v>
+        <v>0.08654413136619632</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2427704764057162</v>
+        <v>0.2446704764057162</v>
       </c>
       <c r="C72">
-        <v>-71.542484283787</v>
+        <v>-75.01719841067441</v>
       </c>
       <c r="D72">
-        <v>75.01751571621297</v>
+        <v>74.30080158932557</v>
       </c>
       <c r="E72">
-        <v>184.66</v>
+        <v>187.418</v>
       </c>
       <c r="F72">
-        <v>193.06</v>
+        <v>195.818</v>
       </c>
       <c r="G72">
         <v>46.5</v>
@@ -7179,28 +7179,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M72">
-        <v>45.523548</v>
+        <v>46.1738844</v>
       </c>
       <c r="N72">
-        <v>-41.58375208163265</v>
+        <v>-42.23408848163265</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-41.58375208163265</v>
+        <v>-42.23408848163265</v>
       </c>
       <c r="Q72">
-        <v>-41.03375208163266</v>
+        <v>-41.68408848163266</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2590349213523873</v>
+        <v>0.2663878496748835</v>
       </c>
       <c r="T72">
-        <v>4.156345511108427</v>
+        <v>4.299667770112166</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.08654413136619632</v>
+        <v>0.0853251999385034</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2446704764057162</v>
+        <v>0.2465704764057162</v>
       </c>
       <c r="C73">
-        <v>-75.01719841067438</v>
+        <v>-78.47834722790611</v>
       </c>
       <c r="D73">
-        <v>74.30080158932557</v>
+        <v>73.59765277209385</v>
       </c>
       <c r="E73">
-        <v>187.4179999999999</v>
+        <v>190.176</v>
       </c>
       <c r="F73">
-        <v>195.818</v>
+        <v>198.576</v>
       </c>
       <c r="G73">
         <v>46.5</v>
@@ -7261,28 +7261,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M73">
-        <v>46.17388439999999</v>
+        <v>46.82422079999999</v>
       </c>
       <c r="N73">
-        <v>-42.23408848163265</v>
+        <v>-42.88442488163265</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-42.23408848163265</v>
+        <v>-42.88442488163265</v>
       </c>
       <c r="Q73">
-        <v>-41.68408848163265</v>
+        <v>-42.33442488163265</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2663878496748834</v>
+        <v>0.2742659871632721</v>
       </c>
       <c r="T73">
-        <v>4.299667770112165</v>
+        <v>4.453227333330456</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.0853251999385034</v>
+        <v>0.0841401277171353</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2465704764057162</v>
+        <v>0.2484704764057162</v>
       </c>
       <c r="C74">
-        <v>-78.47834722790611</v>
+        <v>-81.92631225264429</v>
       </c>
       <c r="D74">
-        <v>73.59765277209385</v>
+        <v>72.90768774735568</v>
       </c>
       <c r="E74">
-        <v>190.176</v>
+        <v>192.934</v>
       </c>
       <c r="F74">
-        <v>198.576</v>
+        <v>201.334</v>
       </c>
       <c r="G74">
         <v>46.5</v>
@@ -7343,28 +7343,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M74">
-        <v>46.82422079999999</v>
+        <v>47.47455719999999</v>
       </c>
       <c r="N74">
-        <v>-42.88442488163265</v>
+        <v>-43.53476128163265</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-42.88442488163265</v>
+        <v>-43.53476128163265</v>
       </c>
       <c r="Q74">
-        <v>-42.33442488163265</v>
+        <v>-42.98476128163265</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2742659871632721</v>
+        <v>0.2827276903915414</v>
       </c>
       <c r="T74">
-        <v>4.453227333330456</v>
+        <v>4.618161679009361</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.0841401277171353</v>
+        <v>0.08298752322785952</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2484704764057162</v>
+        <v>0.2503704764057162</v>
       </c>
       <c r="C75">
-        <v>-81.92631225264429</v>
+        <v>-85.36146082830311</v>
       </c>
       <c r="D75">
-        <v>72.90768774735568</v>
+        <v>72.23053917169685</v>
       </c>
       <c r="E75">
-        <v>192.934</v>
+        <v>195.692</v>
       </c>
       <c r="F75">
-        <v>201.334</v>
+        <v>204.092</v>
       </c>
       <c r="G75">
         <v>46.5</v>
@@ -7425,28 +7425,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M75">
-        <v>47.47455719999999</v>
+        <v>48.12489359999999</v>
       </c>
       <c r="N75">
-        <v>-43.53476128163265</v>
+        <v>-44.18509768163265</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-43.53476128163265</v>
+        <v>-44.18509768163265</v>
       </c>
       <c r="Q75">
-        <v>-42.98476128163265</v>
+        <v>-43.63509768163265</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2827276903915414</v>
+        <v>0.2918402938681391</v>
       </c>
       <c r="T75">
-        <v>4.618161679009361</v>
+        <v>4.795783282048183</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.08298752322785952</v>
+        <v>0.08186607021126679</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2503704764057162</v>
+        <v>0.2522704764057162</v>
       </c>
       <c r="C76">
-        <v>-85.36146082830311</v>
+        <v>-88.78414677670258</v>
       </c>
       <c r="D76">
-        <v>72.23053917169685</v>
+        <v>71.56585322329738</v>
       </c>
       <c r="E76">
-        <v>195.692</v>
+        <v>198.45</v>
       </c>
       <c r="F76">
-        <v>204.092</v>
+        <v>206.85</v>
       </c>
       <c r="G76">
         <v>46.5</v>
@@ -7507,28 +7507,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M76">
-        <v>48.12489359999999</v>
+        <v>48.77522999999999</v>
       </c>
       <c r="N76">
-        <v>-44.18509768163265</v>
+        <v>-44.83543408163265</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-44.18509768163265</v>
+        <v>-44.83543408163265</v>
       </c>
       <c r="Q76">
-        <v>-43.63509768163265</v>
+        <v>-44.28543408163265</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2918402938681391</v>
+        <v>0.3016819056228647</v>
       </c>
       <c r="T76">
-        <v>4.795783282048183</v>
+        <v>4.987614613330111</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.08186607021126679</v>
+        <v>0.08077452260844997</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2522704764057162</v>
+        <v>0.2541704764057162</v>
       </c>
       <c r="C77">
-        <v>-88.78414677670258</v>
+        <v>-92.19471101454363</v>
       </c>
       <c r="D77">
-        <v>71.56585322329738</v>
+        <v>70.91328898545635</v>
       </c>
       <c r="E77">
-        <v>198.45</v>
+        <v>201.208</v>
       </c>
       <c r="F77">
-        <v>206.85</v>
+        <v>209.608</v>
       </c>
       <c r="G77">
         <v>46.5</v>
@@ -7589,28 +7589,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M77">
-        <v>48.77522999999999</v>
+        <v>49.42556639999999</v>
       </c>
       <c r="N77">
-        <v>-44.83543408163265</v>
+        <v>-45.48577048163265</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-44.83543408163265</v>
+        <v>-45.48577048163265</v>
       </c>
       <c r="Q77">
-        <v>-44.28543408163265</v>
+        <v>-44.93577048163265</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3016819056228647</v>
+        <v>0.3123436516904841</v>
       </c>
       <c r="T77">
-        <v>4.987614613330111</v>
+        <v>5.195431888885532</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.08077452260844997</v>
+        <v>0.07971169994254923</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2541704764057162</v>
+        <v>0.2560704764057162</v>
       </c>
       <c r="C78">
-        <v>-92.19471101454363</v>
+        <v>-95.59348213645988</v>
       </c>
       <c r="D78">
-        <v>70.91328898545635</v>
+        <v>70.27251786354007</v>
       </c>
       <c r="E78">
-        <v>201.208</v>
+        <v>203.966</v>
       </c>
       <c r="F78">
-        <v>209.608</v>
+        <v>212.366</v>
       </c>
       <c r="G78">
         <v>46.5</v>
@@ -7671,28 +7671,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M78">
-        <v>49.42556639999999</v>
+        <v>50.07590279999999</v>
       </c>
       <c r="N78">
-        <v>-45.48577048163265</v>
+        <v>-46.13610688163265</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-45.48577048163265</v>
+        <v>-46.13610688163265</v>
       </c>
       <c r="Q78">
-        <v>-44.93577048163265</v>
+        <v>-45.58610688163265</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3123436516904841</v>
+        <v>0.3239325061118095</v>
       </c>
       <c r="T78">
-        <v>5.195431888885532</v>
+        <v>5.421320231880555</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07971169994254923</v>
+        <v>0.07867648306017849</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2560704764057162</v>
+        <v>0.2579704764057162</v>
       </c>
       <c r="C79">
-        <v>-95.59348213645988</v>
+        <v>-98.98077696674258</v>
       </c>
       <c r="D79">
-        <v>70.27251786354007</v>
+        <v>69.64322303325739</v>
       </c>
       <c r="E79">
-        <v>203.966</v>
+        <v>206.724</v>
       </c>
       <c r="F79">
-        <v>212.366</v>
+        <v>215.124</v>
       </c>
       <c r="G79">
         <v>46.5</v>
@@ -7753,28 +7753,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M79">
-        <v>50.07590279999999</v>
+        <v>50.72623919999999</v>
       </c>
       <c r="N79">
-        <v>-46.13610688163265</v>
+        <v>-46.78644328163265</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-46.13610688163265</v>
+        <v>-46.78644328163265</v>
       </c>
       <c r="Q79">
-        <v>-45.58610688163265</v>
+        <v>-46.23644328163265</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3239325061118095</v>
+        <v>0.3365748927532554</v>
       </c>
       <c r="T79">
-        <v>5.421320231880555</v>
+        <v>5.667743878784218</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07867648306017849</v>
+        <v>0.07766781020043267</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2579704764057162</v>
+        <v>0.2598704764057162</v>
       </c>
       <c r="C80">
-        <v>-98.98077696674258</v>
+        <v>-102.3569010816831</v>
       </c>
       <c r="D80">
-        <v>69.64322303325739</v>
+        <v>69.02509891831683</v>
       </c>
       <c r="E80">
-        <v>206.724</v>
+        <v>209.482</v>
       </c>
       <c r="F80">
-        <v>215.124</v>
+        <v>217.882</v>
       </c>
       <c r="G80">
         <v>46.5</v>
@@ -7835,28 +7835,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M80">
-        <v>50.72623919999999</v>
+        <v>51.3765756</v>
       </c>
       <c r="N80">
-        <v>-46.78644328163265</v>
+        <v>-47.43677968163265</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-46.78644328163265</v>
+        <v>-47.43677968163265</v>
       </c>
       <c r="Q80">
-        <v>-46.23644328163265</v>
+        <v>-46.88677968163265</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3365748927532554</v>
+        <v>0.3504213162176962</v>
       </c>
       <c r="T80">
-        <v>5.667743878784218</v>
+        <v>5.937636444440609</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.07766781020043267</v>
+        <v>0.07668467336245244</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2598704764057162</v>
+        <v>0.2617704764057162</v>
       </c>
       <c r="C81">
-        <v>-102.3569010816831</v>
+        <v>-105.722149304345</v>
       </c>
       <c r="D81">
-        <v>69.02509891831683</v>
+        <v>68.41785069565499</v>
       </c>
       <c r="E81">
-        <v>209.482</v>
+        <v>212.24</v>
       </c>
       <c r="F81">
-        <v>217.882</v>
+        <v>220.64</v>
       </c>
       <c r="G81">
         <v>46.5</v>
@@ -7917,28 +7917,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M81">
-        <v>51.3765756</v>
+        <v>52.026912</v>
       </c>
       <c r="N81">
-        <v>-47.43677968163265</v>
+        <v>-48.08711608163265</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-47.43677968163265</v>
+        <v>-48.08711608163265</v>
       </c>
       <c r="Q81">
-        <v>-46.88677968163265</v>
+        <v>-47.53711608163265</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3504213162176962</v>
+        <v>0.365652382028581</v>
       </c>
       <c r="T81">
-        <v>5.937636444440609</v>
+        <v>6.23451826666264</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.07668467336245244</v>
+        <v>0.07572611494542181</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2617704764057162</v>
+        <v>0.2636704764057162</v>
       </c>
       <c r="C82">
-        <v>-105.722149304345</v>
+        <v>-109.0768061734458</v>
       </c>
       <c r="D82">
-        <v>68.41785069565499</v>
+        <v>67.82119382655415</v>
       </c>
       <c r="E82">
-        <v>212.24</v>
+        <v>214.998</v>
       </c>
       <c r="F82">
-        <v>220.64</v>
+        <v>223.398</v>
       </c>
       <c r="G82">
         <v>46.5</v>
@@ -7999,28 +7999,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M82">
-        <v>52.026912</v>
+        <v>52.6772484</v>
       </c>
       <c r="N82">
-        <v>-48.08711608163265</v>
+        <v>-48.73745248163265</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-48.08711608163265</v>
+        <v>-48.73745248163265</v>
       </c>
       <c r="Q82">
-        <v>-47.53711608163265</v>
+        <v>-48.18745248163265</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.365652382028581</v>
+        <v>0.3824867179248221</v>
       </c>
       <c r="T82">
-        <v>6.23451826666264</v>
+        <v>6.562650807013306</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.07572611494542181</v>
+        <v>0.07479122463745369</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2636704764057162</v>
+        <v>0.2655704764057162</v>
       </c>
       <c r="C83">
-        <v>-109.0768061734458</v>
+        <v>-112.4211463879183</v>
       </c>
       <c r="D83">
-        <v>67.82119382655415</v>
+        <v>67.23485361208164</v>
       </c>
       <c r="E83">
-        <v>214.998</v>
+        <v>217.756</v>
       </c>
       <c r="F83">
-        <v>223.398</v>
+        <v>226.156</v>
       </c>
       <c r="G83">
         <v>46.5</v>
@@ -8081,28 +8081,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M83">
-        <v>52.6772484</v>
+        <v>53.3275848</v>
       </c>
       <c r="N83">
-        <v>-48.73745248163265</v>
+        <v>-49.38778888163265</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-48.73745248163265</v>
+        <v>-49.38778888163265</v>
       </c>
       <c r="Q83">
-        <v>-48.18745248163265</v>
+        <v>-48.83778888163265</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3824867179248221</v>
+        <v>0.4011915355873122</v>
       </c>
       <c r="T83">
-        <v>6.562650807013306</v>
+        <v>6.927242518514045</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.07479122463745369</v>
+        <v>0.07387913653211886</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2655704764057162</v>
+        <v>0.2674704764057162</v>
       </c>
       <c r="C84">
-        <v>-112.4211463879183</v>
+        <v>-115.7554352286079</v>
       </c>
       <c r="D84">
-        <v>67.23485361208164</v>
+        <v>66.65856477139207</v>
       </c>
       <c r="E84">
-        <v>217.756</v>
+        <v>220.514</v>
       </c>
       <c r="F84">
-        <v>226.156</v>
+        <v>228.914</v>
       </c>
       <c r="G84">
         <v>46.5</v>
@@ -8163,28 +8163,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M84">
-        <v>53.3275848</v>
+        <v>53.9779212</v>
       </c>
       <c r="N84">
-        <v>-49.38778888163265</v>
+        <v>-50.03812528163265</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-49.38778888163265</v>
+        <v>-50.03812528163265</v>
       </c>
       <c r="Q84">
-        <v>-48.83778888163265</v>
+        <v>-49.48812528163266</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4011915355873122</v>
+        <v>0.4220969200336248</v>
       </c>
       <c r="T84">
-        <v>6.927242518514045</v>
+        <v>7.334727372544283</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.07387913653211886</v>
+        <v>0.07298902645341865</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2674704764057162</v>
+        <v>0.2693704764057162</v>
       </c>
       <c r="C85">
-        <v>-115.7554352286079</v>
+        <v>-119.0799289584679</v>
       </c>
       <c r="D85">
-        <v>66.65856477139207</v>
+        <v>66.09207104153209</v>
       </c>
       <c r="E85">
-        <v>220.514</v>
+        <v>223.272</v>
       </c>
       <c r="F85">
-        <v>228.914</v>
+        <v>231.672</v>
       </c>
       <c r="G85">
         <v>46.5</v>
@@ -8245,28 +8245,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M85">
-        <v>53.9779212</v>
+        <v>54.6282576</v>
       </c>
       <c r="N85">
-        <v>-50.03812528163265</v>
+        <v>-50.68846168163266</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-50.03812528163265</v>
+        <v>-50.68846168163266</v>
       </c>
       <c r="Q85">
-        <v>-49.48812528163266</v>
+        <v>-50.13846168163266</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4220969200336248</v>
+        <v>0.4456154775357263</v>
       </c>
       <c r="T85">
-        <v>7.334727372544283</v>
+        <v>7.793147833328303</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.07298902645341865</v>
+        <v>0.07212010947183023</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2693704764057162</v>
+        <v>0.2712704764057162</v>
       </c>
       <c r="C86">
-        <v>-119.0799289584678</v>
+        <v>-122.3948752025204</v>
       </c>
       <c r="D86">
-        <v>66.09207104153209</v>
+        <v>65.53512479747951</v>
       </c>
       <c r="E86">
-        <v>223.2719999999999</v>
+        <v>226.0299999999999</v>
       </c>
       <c r="F86">
-        <v>231.6719999999999</v>
+        <v>234.4299999999999</v>
       </c>
       <c r="G86">
         <v>46.5</v>
@@ -8327,28 +8327,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M86">
-        <v>54.62825759999999</v>
+        <v>55.27859399999999</v>
       </c>
       <c r="N86">
-        <v>-50.68846168163265</v>
+        <v>-51.33879808163265</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-50.68846168163265</v>
+        <v>-51.33879808163265</v>
       </c>
       <c r="Q86">
-        <v>-50.13846168163265</v>
+        <v>-50.78879808163265</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4456154775357261</v>
+        <v>0.4722698427047746</v>
       </c>
       <c r="T86">
-        <v>7.793147833328297</v>
+        <v>8.312691022216852</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.07212010947183034</v>
+        <v>0.07127163759569111</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2712704764057162</v>
+        <v>0.2731704764057162</v>
       </c>
       <c r="C87">
-        <v>-122.3948752025204</v>
+        <v>-125.700513308767</v>
       </c>
       <c r="D87">
-        <v>65.53512479747951</v>
+        <v>64.98748669123293</v>
       </c>
       <c r="E87">
-        <v>226.0299999999999</v>
+        <v>228.788</v>
       </c>
       <c r="F87">
-        <v>234.4299999999999</v>
+        <v>237.188</v>
       </c>
       <c r="G87">
         <v>46.5</v>
@@ -8409,28 +8409,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M87">
-        <v>55.27859399999999</v>
+        <v>55.92893039999999</v>
       </c>
       <c r="N87">
-        <v>-51.33879808163265</v>
+        <v>-51.98913448163265</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-51.33879808163265</v>
+        <v>-51.98913448163265</v>
       </c>
       <c r="Q87">
-        <v>-50.78879808163265</v>
+        <v>-51.43913448163265</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4722698427047746</v>
+        <v>0.502731974326544</v>
       </c>
       <c r="T87">
-        <v>8.312691022216852</v>
+        <v>8.906454666660911</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.07127163759569111</v>
+        <v>0.07044289762364819</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2731704764057162</v>
+        <v>0.2750704764057161</v>
       </c>
       <c r="C88">
-        <v>-125.700513308767</v>
+        <v>-128.997074691153</v>
       </c>
       <c r="D88">
-        <v>64.98748669123293</v>
+        <v>64.44892530884701</v>
       </c>
       <c r="E88">
-        <v>228.788</v>
+        <v>231.546</v>
       </c>
       <c r="F88">
-        <v>237.188</v>
+        <v>239.946</v>
       </c>
       <c r="G88">
         <v>46.5</v>
@@ -8491,28 +8491,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M88">
-        <v>55.92893039999999</v>
+        <v>56.57926679999999</v>
       </c>
       <c r="N88">
-        <v>-51.98913448163265</v>
+        <v>-52.63947088163265</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-51.98913448163265</v>
+        <v>-52.63947088163265</v>
       </c>
       <c r="Q88">
-        <v>-51.43913448163265</v>
+        <v>-52.08947088163265</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.502731974326544</v>
+        <v>0.5378805877362782</v>
       </c>
       <c r="T88">
-        <v>8.906454666660911</v>
+        <v>9.591566564096366</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.07044289762364819</v>
+        <v>0.06963320914521542</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2750704764057161</v>
+        <v>0.2769704764057162</v>
       </c>
       <c r="C89">
-        <v>-128.997074691153</v>
+        <v>-132.2847831556192</v>
       </c>
       <c r="D89">
-        <v>64.44892530884701</v>
+        <v>63.91921684438071</v>
       </c>
       <c r="E89">
-        <v>231.546</v>
+        <v>234.3039999999999</v>
       </c>
       <c r="F89">
-        <v>239.946</v>
+        <v>242.704</v>
       </c>
       <c r="G89">
         <v>46.5</v>
@@ -8573,28 +8573,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M89">
-        <v>56.57926679999999</v>
+        <v>57.22960319999999</v>
       </c>
       <c r="N89">
-        <v>-52.63947088163265</v>
+        <v>-53.28980728163265</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-52.63947088163265</v>
+        <v>-53.28980728163265</v>
       </c>
       <c r="Q89">
-        <v>-52.08947088163265</v>
+        <v>-52.73980728163265</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5378805877362782</v>
+        <v>0.5788873033809682</v>
       </c>
       <c r="T89">
-        <v>9.591566564096366</v>
+        <v>10.39086377777106</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.06963320914521542</v>
+        <v>0.06884192267765621</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2769704764057162</v>
+        <v>0.2788704764057162</v>
       </c>
       <c r="C90">
-        <v>-132.2847831556192</v>
+        <v>-135.5638552102064</v>
       </c>
       <c r="D90">
-        <v>63.91921684438071</v>
+        <v>63.39814478979361</v>
       </c>
       <c r="E90">
-        <v>234.3039999999999</v>
+        <v>237.062</v>
       </c>
       <c r="F90">
-        <v>242.704</v>
+        <v>245.462</v>
       </c>
       <c r="G90">
         <v>46.5</v>
@@ -8655,28 +8655,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M90">
-        <v>57.22960319999999</v>
+        <v>57.87993959999999</v>
       </c>
       <c r="N90">
-        <v>-53.28980728163265</v>
+        <v>-53.94014368163265</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-53.28980728163265</v>
+        <v>-53.94014368163265</v>
       </c>
       <c r="Q90">
-        <v>-52.73980728163265</v>
+        <v>-53.39014368163265</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5788873033809682</v>
+        <v>0.6273497855065108</v>
       </c>
       <c r="T90">
-        <v>10.39086377777106</v>
+        <v>11.33548775756844</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06884192267765621</v>
+        <v>0.06806841792846907</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2788704764057162</v>
+        <v>0.2807704764057162</v>
       </c>
       <c r="C91">
-        <v>-135.5638552102064</v>
+        <v>-138.8345003601129</v>
       </c>
       <c r="D91">
-        <v>63.39814478979361</v>
+        <v>62.88549963988712</v>
       </c>
       <c r="E91">
-        <v>237.062</v>
+        <v>239.82</v>
       </c>
       <c r="F91">
-        <v>245.462</v>
+        <v>248.22</v>
       </c>
       <c r="G91">
         <v>46.5</v>
@@ -8737,28 +8737,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M91">
-        <v>57.87993959999999</v>
+        <v>58.53027599999999</v>
       </c>
       <c r="N91">
-        <v>-53.94014368163265</v>
+        <v>-54.59048008163265</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-53.94014368163265</v>
+        <v>-54.59048008163265</v>
       </c>
       <c r="Q91">
-        <v>-53.39014368163265</v>
+        <v>-54.04048008163265</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6273497855065108</v>
+        <v>0.6855047640571619</v>
       </c>
       <c r="T91">
-        <v>11.33548775756844</v>
+        <v>12.46903653332528</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06806841792846907</v>
+        <v>0.06731210217370831</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2807704764057162</v>
+        <v>0.2826704764057162</v>
       </c>
       <c r="C92">
-        <v>-138.8345003601129</v>
+        <v>-142.0969213885535</v>
       </c>
       <c r="D92">
-        <v>62.88549963988712</v>
+        <v>62.38107861144651</v>
       </c>
       <c r="E92">
-        <v>239.82</v>
+        <v>242.578</v>
       </c>
       <c r="F92">
-        <v>248.22</v>
+        <v>250.978</v>
       </c>
       <c r="G92">
         <v>46.5</v>
@@ -8819,28 +8819,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M92">
-        <v>58.53027599999999</v>
+        <v>59.1806124</v>
       </c>
       <c r="N92">
-        <v>-54.59048008163265</v>
+        <v>-55.24081648163266</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-54.59048008163265</v>
+        <v>-55.24081648163266</v>
       </c>
       <c r="Q92">
-        <v>-54.04048008163265</v>
+        <v>-54.69081648163266</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6855047640571619</v>
+        <v>0.7565830711746243</v>
       </c>
       <c r="T92">
-        <v>12.46903653332528</v>
+        <v>13.85448503702809</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06731210217370831</v>
+        <v>0.06657240874322801</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2826704764057162</v>
+        <v>0.2845704764057162</v>
       </c>
       <c r="C93">
-        <v>-142.0969213885535</v>
+        <v>-145.3513146242077</v>
       </c>
       <c r="D93">
-        <v>62.38107861144651</v>
+        <v>61.88468537579223</v>
       </c>
       <c r="E93">
-        <v>242.578</v>
+        <v>245.336</v>
       </c>
       <c r="F93">
-        <v>250.978</v>
+        <v>253.736</v>
       </c>
       <c r="G93">
         <v>46.5</v>
@@ -8901,28 +8901,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M93">
-        <v>59.1806124</v>
+        <v>59.83094879999999</v>
       </c>
       <c r="N93">
-        <v>-55.24081648163266</v>
+        <v>-55.89115288163265</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-55.24081648163266</v>
+        <v>-55.89115288163265</v>
       </c>
       <c r="Q93">
-        <v>-54.69081648163266</v>
+        <v>-55.34115288163265</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7565830711746243</v>
+        <v>0.8454309550714526</v>
       </c>
       <c r="T93">
-        <v>13.85448503702809</v>
+        <v>15.58629566665661</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.06657240874322801</v>
+        <v>0.06584879560471457</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2845704764057162</v>
+        <v>0.2864704764057162</v>
       </c>
       <c r="C94">
-        <v>-145.3513146242077</v>
+        <v>-148.5978701960004</v>
       </c>
       <c r="D94">
-        <v>61.88468537579223</v>
+        <v>61.39612980399957</v>
       </c>
       <c r="E94">
-        <v>245.336</v>
+        <v>248.094</v>
       </c>
       <c r="F94">
-        <v>253.736</v>
+        <v>256.494</v>
       </c>
       <c r="G94">
         <v>46.5</v>
@@ -8983,28 +8983,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M94">
-        <v>59.83094879999999</v>
+        <v>60.48128519999999</v>
       </c>
       <c r="N94">
-        <v>-55.89115288163265</v>
+        <v>-56.54148928163265</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-55.89115288163265</v>
+        <v>-56.54148928163265</v>
       </c>
       <c r="Q94">
-        <v>-55.34115288163265</v>
+        <v>-55.99148928163265</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8454309550714526</v>
+        <v>0.9596639486530889</v>
       </c>
       <c r="T94">
-        <v>15.58629566665661</v>
+        <v>17.81290933332184</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.06584879560471457</v>
+        <v>0.06514074403907255</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2864704764057162</v>
+        <v>0.2883704764057162</v>
       </c>
       <c r="C95">
-        <v>-148.5978701960004</v>
+        <v>-151.8367722759076</v>
       </c>
       <c r="D95">
-        <v>61.39612980399957</v>
+        <v>60.91522772409235</v>
       </c>
       <c r="E95">
-        <v>248.094</v>
+        <v>250.8519999999999</v>
       </c>
       <c r="F95">
-        <v>256.494</v>
+        <v>259.252</v>
       </c>
       <c r="G95">
         <v>46.5</v>
@@ -9065,28 +9065,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M95">
-        <v>60.48128519999999</v>
+        <v>61.13162159999999</v>
       </c>
       <c r="N95">
-        <v>-56.54148928163265</v>
+        <v>-57.19182568163264</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-56.54148928163265</v>
+        <v>-57.19182568163264</v>
       </c>
       <c r="Q95">
-        <v>-55.99148928163265</v>
+        <v>-56.64182568163265</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9596639486530889</v>
+        <v>1.111974606761937</v>
       </c>
       <c r="T95">
-        <v>17.81290933332184</v>
+        <v>20.78172755554215</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.06514074403907255</v>
+        <v>0.06444775740035902</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2883704764057162</v>
+        <v>0.2902704764057162</v>
       </c>
       <c r="C96">
-        <v>-151.8367722759076</v>
+        <v>-155.0681993104413</v>
       </c>
       <c r="D96">
-        <v>60.91522772409235</v>
+        <v>60.44180068955874</v>
       </c>
       <c r="E96">
-        <v>250.8519999999999</v>
+        <v>253.61</v>
       </c>
       <c r="F96">
-        <v>259.252</v>
+        <v>262.01</v>
       </c>
       <c r="G96">
         <v>46.5</v>
@@ -9147,28 +9147,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M96">
-        <v>61.13162159999999</v>
+        <v>61.781958</v>
       </c>
       <c r="N96">
-        <v>-57.19182568163264</v>
+        <v>-57.84216208163266</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-57.19182568163264</v>
+        <v>-57.84216208163266</v>
       </c>
       <c r="Q96">
-        <v>-56.64182568163265</v>
+        <v>-57.29216208163266</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.111974606761937</v>
+        <v>1.325209528114325</v>
       </c>
       <c r="T96">
-        <v>20.78172755554215</v>
+        <v>24.93807306665059</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.06444775740035902</v>
+        <v>0.06376935995403943</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2902704764057162</v>
+        <v>0.2921704764057162</v>
       </c>
       <c r="C97">
-        <v>-155.0681993104413</v>
+        <v>-158.2923242414214</v>
       </c>
       <c r="D97">
-        <v>60.44180068955874</v>
+        <v>59.97567575857859</v>
       </c>
       <c r="E97">
-        <v>253.61</v>
+        <v>256.368</v>
       </c>
       <c r="F97">
-        <v>262.01</v>
+        <v>264.768</v>
       </c>
       <c r="G97">
         <v>46.5</v>
@@ -9229,28 +9229,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M97">
-        <v>61.781958</v>
+        <v>62.4322944</v>
       </c>
       <c r="N97">
-        <v>-57.84216208163266</v>
+        <v>-58.49249848163265</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-57.84216208163266</v>
+        <v>-58.49249848163265</v>
       </c>
       <c r="Q97">
-        <v>-57.29216208163266</v>
+        <v>-57.94249848163265</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.325209528114325</v>
+        <v>1.645061910142907</v>
       </c>
       <c r="T97">
-        <v>24.93807306665059</v>
+        <v>31.17259133331325</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.06376935995403943</v>
+        <v>0.06310509578785151</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2921704764057162</v>
+        <v>0.2940704764057162</v>
       </c>
       <c r="C98">
-        <v>-158.2923242414214</v>
+        <v>-161.5093147166122</v>
       </c>
       <c r="D98">
-        <v>59.97567575857859</v>
+        <v>59.51668528338782</v>
       </c>
       <c r="E98">
-        <v>256.368</v>
+        <v>259.126</v>
       </c>
       <c r="F98">
-        <v>264.768</v>
+        <v>267.526</v>
       </c>
       <c r="G98">
         <v>46.5</v>
@@ -9311,28 +9311,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M98">
-        <v>62.4322944</v>
+        <v>63.08263079999999</v>
       </c>
       <c r="N98">
-        <v>-58.49249848163265</v>
+        <v>-59.14283488163264</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-58.49249848163265</v>
+        <v>-59.14283488163264</v>
       </c>
       <c r="Q98">
-        <v>-57.94249848163265</v>
+        <v>-58.59283488163265</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.645061910142903</v>
+        <v>2.178149213523871</v>
       </c>
       <c r="T98">
-        <v>31.17259133331317</v>
+        <v>41.56345511108422</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.06310509578785151</v>
+        <v>0.06245452779003857</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2940704764057162</v>
+        <v>0.2959704764057162</v>
       </c>
       <c r="C99">
-        <v>-161.5093147166122</v>
+        <v>-164.7193332907585</v>
       </c>
       <c r="D99">
-        <v>59.51668528338782</v>
+        <v>59.06466670924142</v>
       </c>
       <c r="E99">
-        <v>259.126</v>
+        <v>261.884</v>
       </c>
       <c r="F99">
-        <v>267.526</v>
+        <v>270.2839999999999</v>
       </c>
       <c r="G99">
         <v>46.5</v>
@@ -9393,28 +9393,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M99">
-        <v>63.08263079999999</v>
+        <v>63.73296719999999</v>
       </c>
       <c r="N99">
-        <v>-59.14283488163264</v>
+        <v>-59.79317128163265</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-59.14283488163264</v>
+        <v>-59.79317128163265</v>
       </c>
       <c r="Q99">
-        <v>-58.59283488163265</v>
+        <v>-59.24317128163265</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.178149213523871</v>
+        <v>3.244323820285806</v>
       </c>
       <c r="T99">
-        <v>41.56345511108422</v>
+        <v>62.34518266662634</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.06245452779003857</v>
+        <v>0.06181723669014028</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2959704764057162</v>
+        <v>0.2978704764057162</v>
       </c>
       <c r="C100">
-        <v>-164.7193332907585</v>
+        <v>-167.9225376175316</v>
       </c>
       <c r="D100">
-        <v>59.06466670924142</v>
+        <v>58.61946238246841</v>
       </c>
       <c r="E100">
-        <v>261.884</v>
+        <v>264.642</v>
       </c>
       <c r="F100">
-        <v>270.2839999999999</v>
+        <v>273.042</v>
       </c>
       <c r="G100">
         <v>46.5</v>
@@ -9475,28 +9475,28 @@
         <v>3.939795918367347</v>
       </c>
       <c r="M100">
-        <v>63.73296719999999</v>
+        <v>64.38330359999999</v>
       </c>
       <c r="N100">
-        <v>-59.79317128163265</v>
+        <v>-60.44350768163265</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-59.79317128163265</v>
+        <v>-60.44350768163265</v>
       </c>
       <c r="Q100">
-        <v>-59.24317128163265</v>
+        <v>-59.89350768163265</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.244323820285806</v>
+        <v>6.442847640571613</v>
       </c>
       <c r="T100">
-        <v>62.34518266662634</v>
+        <v>124.6903653332527</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.06181723669014028</v>
+        <v>0.06119282015791661</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2978704764057162</v>
-      </c>
-      <c r="C101">
-        <v>-167.9225376175316</v>
-      </c>
-      <c r="D101">
-        <v>58.61946238246841</v>
-      </c>
-      <c r="E101">
-        <v>264.642</v>
-      </c>
-      <c r="F101">
-        <v>273.042</v>
-      </c>
-      <c r="G101">
-        <v>46.5</v>
-      </c>
-      <c r="H101">
-        <v>267.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.489795918367347</v>
-      </c>
-      <c r="K101">
-        <v>0.5500000000000003</v>
-      </c>
-      <c r="L101">
-        <v>3.939795918367347</v>
-      </c>
-      <c r="M101">
-        <v>64.38330359999999</v>
-      </c>
-      <c r="N101">
-        <v>-60.44350768163265</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-60.44350768163265</v>
-      </c>
-      <c r="Q101">
-        <v>-59.89350768163265</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.442847640571613</v>
-      </c>
-      <c r="T101">
-        <v>124.6903653332527</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.06119282015791661</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
